--- a/data/ontap121.xlsx
+++ b/data/ontap121.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tdtam\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC25BA9F-C57D-44C6-B4A0-2E8ED430510E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB24E835-4FEA-4EF1-80D3-5C2E456E9C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="1068">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1714" uniqueCount="1171">
   <si>
     <t>Họ tên</t>
   </si>
@@ -1121,18 +1121,6 @@
     <t>Xét tình huống gửi dữ liệu qua Internet:</t>
   </si>
   <si>
-    <t>a) Giao thức mạng quy định cách thức giao tiếp giữa các đối tượng truyền nhận dữ liệu.</t>
-  </si>
-  <si>
-    <t>b) Khi hai máy không cùng LAN, router hỗ trợ chuyển tiếp dữ liệu dựa trên IP.</t>
-  </si>
-  <si>
-    <t>c) Nếu gói đến không có mục trong bảng định tuyến tĩnh nhưng có cổng mặc định, router có thể chuyển theo cổng mặc định.</t>
-  </si>
-  <si>
-    <t>d) Nếu máy nhận ở LAN khác, máy gửi có thể bỏ qua router vì chỉ cần biết MAC của máy nhận từ đầu.</t>
-  </si>
-  <si>
     <t>ĐĐĐS</t>
   </si>
   <si>
@@ -3237,13 +3225,334 @@
   </si>
   <si>
     <t>Q153</t>
+  </si>
+  <si>
+    <t>Đánh dấu đúng hoặc sai về một số lĩnh vực nghiên cứu phát triển AI?</t>
+  </si>
+  <si>
+    <t>Học máy là lĩnh vực nghiên cứu làm cho máy tính có khả năng học từ dữ liệu thu được.</t>
+  </si>
+  <si>
+    <t>Giao thức mạng quy định cách thức giao tiếp giữa các đối tượng truyền nhận dữ liệu.</t>
+  </si>
+  <si>
+    <t>Khi hai máy không cùng LAN, router hỗ trợ chuyển tiếp dữ liệu dựa trên IP.</t>
+  </si>
+  <si>
+    <t>Nếu gói đến không có mục trong bảng định tuyến tĩnh nhưng có cổng mặc định, router có thể chuyển theo cổng mặc định.</t>
+  </si>
+  <si>
+    <t>Nếu máy nhận ở LAN khác, máy gửi có thể bỏ qua router vì chỉ cần biết MAC của máy nhận từ đầu.</t>
+  </si>
+  <si>
+    <t>Xử lý ngôn ngữ tự nhiên là nghiên cứu các mô hình ngôn ngữ để máy tính và con người giao tiếp với nhau</t>
+  </si>
+  <si>
+    <t>Thị giác máy tính là lĩnh vực nghiên cứu phương pháp thu nhận và phân tích nhận dạng hình ảnh</t>
+  </si>
+  <si>
+    <t>AI hẹp là AI có khả năng tự học từ dữ liệu mới.</t>
+  </si>
+  <si>
+    <t>AI đang phát triển nhanh chóng và ứng dụng vào hầu hết các lĩnh vực như giáo dục, y tế, tài chính, nông nghiệp, giao thông,…</t>
+  </si>
+  <si>
+    <t>Nhận dạng khuôn mặt phổ biến trong rất nhiều ứng dụng: sử dụng khuôn mặt để mở khoá điện thoại thông minh, xác thực khuôn mặt trong các ứng dụng ngân hàng thông minh, điểm danh trong các ứng dụng học trực tuyến.</t>
+  </si>
+  <si>
+    <t>Trợ lí ảo được xây dựng để nhận dạng và hiểu giọng nói của con người.</t>
+  </si>
+  <si>
+    <t>Các nhà khoa học tại Viện Công nghệ Massachusetts đã tạo ra ứng dụng Sybil dựa trên AI để phát hiện dấu hiệu bệnh ung thư máu.</t>
+  </si>
+  <si>
+    <t>Nhiều ứng dụng dạy ngôn ngữ sử dụng AI và nhận dạng khuôn mặt để đánh giá khả năng ngôn ngữ của người học</t>
+  </si>
+  <si>
+    <t>ĐĐSS</t>
+  </si>
+  <si>
+    <t>Mô hình AI trong lĩnh vực thị giác máy tính cho phép các thiết bị thông minh nhận dạng chữ viết tay.</t>
+  </si>
+  <si>
+    <t>Trợ lý ảo là một công nghệ AI được xây dựng để nhận dạng và hiểu giọng nói của con người</t>
+  </si>
+  <si>
+    <t>SĐĐĐ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI đã có những tác động mạnh mẽ trong các lĩnh vực khoa học công nghệ và đời sống. </t>
+  </si>
+  <si>
+    <t>AI giúp cải thiện dịch vụ nhằm thu hút và nâng cao trải nghiệm của khách hàng.</t>
+  </si>
+  <si>
+    <t>Các hệ thống AI trong y tế có thể thay thế hoàn toàn bác sĩ trong quá trình chẩn đoán</t>
+  </si>
+  <si>
+    <t>AI không có vai trò gì trong lĩnh vực tài chính</t>
+  </si>
+  <si>
+    <t>AI có khả năng giải quyết các vấn đề phức tạp trong lập trình</t>
+  </si>
+  <si>
+    <t>Có những cảnh báo về AI trong tương lai. Hãy đánh dấu Đúng hoặc Sai cho các phát biểu sau:</t>
+  </si>
+  <si>
+    <t>Dữ liệu huấn luyện thiên vị có thể gây ra các vấn đề đạo đức trong AI.</t>
+  </si>
+  <si>
+    <t>AI hoàn toàn không ảnh hưởng đến quyền riêng tư cá nhân</t>
+  </si>
+  <si>
+    <t>AI có thể tạo ra các cuộc tấn công mạng thông minh và khó bị phát hiện.</t>
+  </si>
+  <si>
+    <t>AI chỉ tạo ra công việc mới mà không thay thế các công việc hiện tại.</t>
+  </si>
+  <si>
+    <t>ĐSĐS</t>
+  </si>
+  <si>
+    <t>Khi so sánh về đặc điểm và chức năng giữa Switch và Hub trong mạng LAN, mỗi nhận định sau đây là Đúng hay Sai?</t>
+  </si>
+  <si>
+    <t>Switch là thiết bị chuyên dùng cho mạng không dây, trong khi Hub chỉ dùng cho mạng có dây.</t>
+  </si>
+  <si>
+    <t>Hub có khả năng kiểm tra địa chỉ và chuyển tiếp dữ liệu có chọn lọc, còn Switch gửi dữ liệu đồng thời đến tất cả các cổng.</t>
+  </si>
+  <si>
+    <t>Switch chuyển tiếp khung dữ liệu đến đúng cổng của thiết bị nhận, trong khi Hub phát tán tín hiệu đến tất cả các cổng còn lại</t>
+  </si>
+  <si>
+    <t>Hub có tốc độ truyền tải nhanh hơn và khả năng bảo mật thông tin cao hơn so với Switch</t>
+  </si>
+  <si>
+    <t>Tòa nhà của một công ty có một số phòng làm việc. Mỗi phòng có không quá 10 máy tính, được kết nối với nhau thông qua Switch tạo thành một mạng LAN. Công ty cần kết nối các mạng LAN này với nhau để tạo thành một mạng cục bộ duy nhất. Sau khi thảo luận, một số nhân viên của công ty đưa ra các nhận định sau:</t>
+  </si>
+  <si>
+    <t>Mạng cục bộ của công ty là mạng WAN</t>
+  </si>
+  <si>
+    <t>Có thể sử dụng Switch loại 16 cổng để kết nối các máy tính trong mỗi phòng làm việc</t>
+  </si>
+  <si>
+    <t>Để máy tính trong các phòng làm việc truy cập được Internet thì chỉ cần lắp đặt thêm một Modem mà không cần phải đăng ký với nhà cung cấp dịch vụ Internet.</t>
+  </si>
+  <si>
+    <t>Để các nhân viên có thể sử dụng điện thoại thông minh kết nối được vào mạng cục bộ của công ty qua Wi-Fi, có thể lắp đặt cho mỗi phòng một Access Point và kết nối thiết bị này với Switch ở phòng đó.</t>
+  </si>
+  <si>
+    <t>SĐSĐ</t>
+  </si>
+  <si>
+    <t>Một gia đình chuyển đến căn nhà mới có bốn tầng. Họ được nhà cung cấp dịch vụ viễn thông lắp đặt một Modem để sử dụng Internet trong nhà. Các thành viên trong gia đình thường sử dụng điện thoại thông minh để truy cập Internet, tuy nhiên, tín hiệu Internet không ổn định tại một số phòng. Hơn nữa, gia đình còn có nhu cầu sử dụng Internet trên các máy tính để bàn không có chức năng kết nối mạng không dây. Các thành viên trong gia đình đã đưa ra các ý kiến sau:</t>
+  </si>
+  <si>
+    <t>Việc truy cập Internet bằng điện thoại thông minh mà không dùng dữ liệu mạng di động chứng tỏ Modem của gia đình đã được tích hợp chức năng phát Wi-Fi</t>
+  </si>
+  <si>
+    <t>Để tránh tình trạng tín hiệu Internet không ổn định trong một số phòng, có thể dùng thêm Access Point để kết nối với Modem và đặt Access Point này ở vị trí gần các phòng đó.</t>
+  </si>
+  <si>
+    <t>Nếu gia đình muốn sử dụng Internet bằng máy tính để bàn thì cách đơn giản nhất là dùng cáp mạng để kết nối giữa máy tính đó với Modem.</t>
+  </si>
+  <si>
+    <t>Để tất cả các máy tính để bàn truy cập được Internet, gia đình cần kết nối các máy tính đó với nhau thông qua một Switch nhưng không kết nối Switch với Modem</t>
+  </si>
+  <si>
+    <t>Chọn đúng hoặc sai cho từng câu sau về giao thức mạng và TCP/IP:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giao thức TCP/IP bao gồm hai phần chính là TCP và UDP. </t>
+  </si>
+  <si>
+    <t>Giao thức TCP đảm bảo việc truyền dữ liệu tin cậy, không bị mất mát và đúng thứ tự.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Giao thức HTTP được sử dụng để gửi email giữa các thiết bị. </t>
+  </si>
+  <si>
+    <t>Giao thức HTTPS có lớp mã hóa giúp truyền dữ liệu an toàn.</t>
+  </si>
+  <si>
+    <t>Khi nói về vai trò và đặc điểm của giao thức IP (Internet Protocol) trong bộ giao thức TCP/IP, mỗi nhận định sau đây là Đúng hay Sai?</t>
+  </si>
+  <si>
+    <t>IP chịu trách nhiệm kiểm tra lỗi dữ liệu trên đường truyền và tự động yêu cầu gửi lại các gói tin bị mất mát.</t>
+  </si>
+  <si>
+    <t>Vai trò chính của IP là đánh địa chỉ logic và định tuyến các gói tin từ thiết bị gửi đến thiết bị nhận qua các mạng khác nhau.</t>
+  </si>
+  <si>
+    <t>Giao thức IP tích hợp sẵn cơ chế mã hóa dữ liệu mặc định để bảo mật các giao dịch thanh toán trực tuyến của người dùng.</t>
+  </si>
+  <si>
+    <t>IP hoạt động ở tầng Mạng (Internet/Network layer) và không thiết lập kênh truyền kết nối chuyên biệt (connectionless) trước khi gửi dữ liệu.</t>
+  </si>
+  <si>
+    <t>Các phát biểu sau đúng hay sai khi thực hiện chia sẻ và sử dụng tài nguyên dùng chung trong mạng cục bộ trên Windows?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để chia sẻ ổ đĩa, người dùng nhấp chuột phải vào ổ đĩa, chọn Properties, vào thẻ Sharing, chọn Advanced Sharing và kích hoạt tính năng chia sẻ. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để chia sẻ một thư mục, người dùng nhấp chuột phải vào thư mục đó, chọn Properties, rồi chọn thẻ Sharing. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi chia sẻ ổ đĩa qua mạng, người dùng không thể thiết lập phân quyền truy cập cho các tài khoản hoặc nhóm người dùng khác. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máy tính kết nối trực tiếp với máy in không cần cài đặt trình điều khiển (driver) vẫn có thể chia sẻ máy in đó cho toàn mạng. </t>
+  </si>
+  <si>
+    <t>Khi thực hiện chia sẻ máy in và sử dụng máy in mạng trong hệ điều hành Windows, các phát biểu sau là Đúng hay Sai?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Máy tính kết nối trực tiếp với máy in đóng vai trò là máy chủ cung cấp dịch vụ in (Print Server). </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Các máy tính khác trong mạng chỉ có thể in được nếu máy tính chia sẻ máy in đang bật và kết nối mạng. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Để chia sẻ máy in, người dùng mở thẻ Sharing trong cửa sổ Printer properties và chọn Share this printer. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khi kết nối máy in dùng chung qua mạng, người dùng bắt buộc phải nhập chính xác địa chỉ MAC của máy in đó. (Sai - chỉ cần duyệt tìm tên máy tính chia sẻ hoặc tên máy in) </t>
+  </si>
+  <si>
+    <t>Để nhóm học sinh có thể vừa xem tài liệu, vừa nộp bài tập và sửa đổi nội dung tệp tin trong thư mục dùng chung DỰ ÁN trên mạng cục bộ, mỗi nhận định sau đây là Đúng hay Sai?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người quản trị cần thiết lập mức phân quyền là Read cho nhóm học sinh. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người quản trị cần thiết lập mức phân quyền là Read/Write cho nhóm học sinh. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Người quản trị nên bật tính năng bảo vệ bằng mật khẩu (Turn on password protected sharing) nhưng không cần cung cấp tài khoản cho học sinh. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Việc thiết lập phân quyền chia sẻ được thực hiện thông qua thẻ Sharing trong cửa sổ Properties của thư mục DỰ ÁN. </t>
+  </si>
+  <si>
+    <t>Trong bối cảnh hội nhập toàn cầu hiện nay, sự bùng nổ của công nghệ thông tin và truyền thông đã góp phần thay đổi phương thức giao tiếp trong xã hội.</t>
+  </si>
+  <si>
+    <t>Không gian mạng cho phép con người giao tiếp với nhau thông qua các phần mềm và dịch vụ giao tiếp trực tuyến như mạng xã hội, thư giấy, ứng dụng nhắn tin, gọi điện thoại video,…</t>
+  </si>
+  <si>
+    <t>Giao tiếp trực tuyến có thể được thực hiện mọi nơi, mọi lúc, miễn là có kết nối mạng.</t>
+  </si>
+  <si>
+    <t>Giao tiếp trong không gian mạng có thể gây khó khăn trong việc truyền đạt cảm xúc và dẫn đến những hiểu lầm không đáng có.</t>
+  </si>
+  <si>
+    <t>“Tránh gửi nội dung thư rác hoặc quảng cáo không liên quan đến nội dung chính của cuộc trò chuyện” thể hiện khía cạnh tôn trọng trong việc ứng xử nhân văn trong không gian mạng.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Một người lạ nhắn tin bắt chuyện qua mạng xã hội và giới thiệu cơ hội “việc nhẹ lương cao” cho một học sinh. Tuy nhiên, người này yêu cầu học sinh phải chuyển khoản trước một số tiền đặt cọc để giữ chỗ nhận việc. Để đảm bảo an toàn cho bản thân trên không gian mạng, mỗi nhận định sau đây về cách ứng xử của bạn học sinh là Đúng hay Sai? </t>
+  </si>
+  <si>
+    <t>Nộp ngay khoản tiền đặt cọc theo yêu cầu để không bỏ lỡ cơ hội việc làm hấp dẫn.</t>
+  </si>
+  <si>
+    <t>Chủ động xác minh kỹ thông tin về doanh nghiệp hoặc đối tượng tuyển dụng qua các kênh chính thống trước khi đưa ra quyết định.</t>
+  </si>
+  <si>
+    <t>Bỏ qua tin nhắn, chặn liên hệ từ tài khoản lạ và cảnh báo cho bạn bè, người thân về dấu hiệu lừa đảo tương tự.</t>
+  </si>
+  <si>
+    <t>Nếu nhận thấy dấu hiệu lừa đảo chiếm đoạt tài sản rõ ràng, học sinh nên thu thập bằng chứng tin nhắn và cùng gia đình trình báo cho cơ quan công an.</t>
+  </si>
+  <si>
+    <t>Q154</t>
+  </si>
+  <si>
+    <t>Q155</t>
+  </si>
+  <si>
+    <t>Q156</t>
+  </si>
+  <si>
+    <t>Q157</t>
+  </si>
+  <si>
+    <t>Q158</t>
+  </si>
+  <si>
+    <t>Q159</t>
+  </si>
+  <si>
+    <t>Q160</t>
+  </si>
+  <si>
+    <t>Q161</t>
+  </si>
+  <si>
+    <t>Q162</t>
+  </si>
+  <si>
+    <t>Q163</t>
+  </si>
+  <si>
+    <t>Q164</t>
+  </si>
+  <si>
+    <t>Q165</t>
+  </si>
+  <si>
+    <t>Q166</t>
+  </si>
+  <si>
+    <t>Q167</t>
+  </si>
+  <si>
+    <t>Q168</t>
+  </si>
+  <si>
+    <t>Nền tảng AI nào do OpenAI phát triển, có khả năng trò chuyện và hỗ trợ tạo nội dung?</t>
+  </si>
+  <si>
+    <t>ChatGPT</t>
+  </si>
+  <si>
+    <t>Công nghệ AI nào của Google có thể hỗ trợ người dùng tìm kiếm thông tin, tạo nội dung và giải đáp câu hỏi?</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Trợ lý AI nào do Anthropic phát triển, có thể hỗ trợ viết nội dung, phân tích tài liệu và lập trình?</t>
+  </si>
+  <si>
+    <t>Claude</t>
+  </si>
+  <si>
+    <t>Trợ lý AI nào do công ty xAI phát triển, gắn liền với nền tảng mạng xã hội X?</t>
+  </si>
+  <si>
+    <t>Grok</t>
+  </si>
+  <si>
+    <t>Q169</t>
+  </si>
+  <si>
+    <t>Q170</t>
+  </si>
+  <si>
+    <t>Q171</t>
+  </si>
+  <si>
+    <t>Q172</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3274,34 +3583,34 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
       <color rgb="FF333333"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
     <font>
       <b/>
-      <sz val="10"/>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
       <family val="1"/>
@@ -3352,7 +3661,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3365,10 +3674,10 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3377,32 +3686,20 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3767,13 +4064,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B179"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="24" customHeight="1">
+    <row r="1" spans="1:2" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3781,7 +4078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>169</v>
       </c>
@@ -3789,7 +4086,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>171</v>
       </c>
@@ -3797,7 +4094,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>172</v>
       </c>
@@ -3805,7 +4102,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>173</v>
       </c>
@@ -3813,7 +4110,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>174</v>
       </c>
@@ -3821,7 +4118,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>175</v>
       </c>
@@ -3829,7 +4126,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>176</v>
       </c>
@@ -3837,7 +4134,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>177</v>
       </c>
@@ -3845,7 +4142,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>178</v>
       </c>
@@ -3853,7 +4150,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>179</v>
       </c>
@@ -3861,7 +4158,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>180</v>
       </c>
@@ -3869,7 +4166,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="3" t="s">
         <v>181</v>
       </c>
@@ -3877,7 +4174,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>182</v>
       </c>
@@ -3885,7 +4182,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>183</v>
       </c>
@@ -3893,7 +4190,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>184</v>
       </c>
@@ -3901,7 +4198,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>185</v>
       </c>
@@ -3909,7 +4206,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>186</v>
       </c>
@@ -3917,7 +4214,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>187</v>
       </c>
@@ -3925,7 +4222,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="20" spans="1:2">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>188</v>
       </c>
@@ -3933,7 +4230,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:2">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>189</v>
       </c>
@@ -3941,7 +4238,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="22" spans="1:2">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>190</v>
       </c>
@@ -3949,7 +4246,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="23" spans="1:2">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>191</v>
       </c>
@@ -3957,7 +4254,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="24" spans="1:2">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>192</v>
       </c>
@@ -3965,7 +4262,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="25" spans="1:2">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>193</v>
       </c>
@@ -3973,7 +4270,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="26" spans="1:2">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>194</v>
       </c>
@@ -3981,7 +4278,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="27" spans="1:2">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>195</v>
       </c>
@@ -3989,7 +4286,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="28" spans="1:2">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>196</v>
       </c>
@@ -3997,7 +4294,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="29" spans="1:2">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>197</v>
       </c>
@@ -4005,7 +4302,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="30" spans="1:2">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>198</v>
       </c>
@@ -4013,7 +4310,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="31" spans="1:2">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>199</v>
       </c>
@@ -4021,7 +4318,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="32" spans="1:2">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>200</v>
       </c>
@@ -4029,7 +4326,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="33" spans="1:2">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>201</v>
       </c>
@@ -4037,7 +4334,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="34" spans="1:2">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>202</v>
       </c>
@@ -4045,7 +4342,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="35" spans="1:2">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>203</v>
       </c>
@@ -4053,7 +4350,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:2">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>204</v>
       </c>
@@ -4061,7 +4358,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="37" spans="1:2">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>205</v>
       </c>
@@ -4069,7 +4366,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="38" spans="1:2">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>206</v>
       </c>
@@ -4077,7 +4374,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="39" spans="1:2">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>207</v>
       </c>
@@ -4085,7 +4382,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="40" spans="1:2">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>208</v>
       </c>
@@ -4093,7 +4390,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="41" spans="1:2">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>209</v>
       </c>
@@ -4101,7 +4398,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="42" spans="1:2">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>210</v>
       </c>
@@ -4109,7 +4406,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="43" spans="1:2">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>211</v>
       </c>
@@ -4117,7 +4414,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="44" spans="1:2">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>212</v>
       </c>
@@ -4125,7 +4422,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="45" spans="1:2">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>213</v>
       </c>
@@ -4133,7 +4430,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="46" spans="1:2">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>214</v>
       </c>
@@ -4141,7 +4438,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="47" spans="1:2">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>215</v>
       </c>
@@ -4149,7 +4446,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="48" spans="1:2">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>217</v>
       </c>
@@ -4157,7 +4454,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>218</v>
       </c>
@@ -4165,7 +4462,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>219</v>
       </c>
@@ -4173,7 +4470,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>220</v>
       </c>
@@ -4181,7 +4478,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>221</v>
       </c>
@@ -4189,7 +4486,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -4197,7 +4494,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>223</v>
       </c>
@@ -4205,7 +4502,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>224</v>
       </c>
@@ -4213,7 +4510,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="56" spans="1:2">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>225</v>
       </c>
@@ -4221,7 +4518,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>226</v>
       </c>
@@ -4229,7 +4526,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>227</v>
       </c>
@@ -4237,7 +4534,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>228</v>
       </c>
@@ -4245,7 +4542,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>229</v>
       </c>
@@ -4253,7 +4550,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="61" spans="1:2">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>230</v>
       </c>
@@ -4261,7 +4558,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>231</v>
       </c>
@@ -4269,7 +4566,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>232</v>
       </c>
@@ -4277,7 +4574,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>233</v>
       </c>
@@ -4285,7 +4582,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="65" spans="1:2">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>234</v>
       </c>
@@ -4293,7 +4590,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="66" spans="1:2">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>235</v>
       </c>
@@ -4301,7 +4598,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="67" spans="1:2">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>236</v>
       </c>
@@ -4309,7 +4606,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="68" spans="1:2">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>237</v>
       </c>
@@ -4317,7 +4614,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="69" spans="1:2">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>238</v>
       </c>
@@ -4325,7 +4622,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="70" spans="1:2">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>239</v>
       </c>
@@ -4333,7 +4630,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="71" spans="1:2">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>240</v>
       </c>
@@ -4341,7 +4638,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="72" spans="1:2">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>241</v>
       </c>
@@ -4349,7 +4646,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="73" spans="1:2">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>242</v>
       </c>
@@ -4357,7 +4654,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="74" spans="1:2">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>243</v>
       </c>
@@ -4365,7 +4662,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="75" spans="1:2">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>244</v>
       </c>
@@ -4373,7 +4670,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:2">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>245</v>
       </c>
@@ -4381,7 +4678,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="77" spans="1:2">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>246</v>
       </c>
@@ -4389,7 +4686,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="78" spans="1:2">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>247</v>
       </c>
@@ -4397,7 +4694,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="79" spans="1:2">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>248</v>
       </c>
@@ -4405,7 +4702,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="80" spans="1:2">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>249</v>
       </c>
@@ -4413,7 +4710,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="81" spans="1:2">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>250</v>
       </c>
@@ -4421,7 +4718,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="82" spans="1:2">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>251</v>
       </c>
@@ -4429,7 +4726,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:2">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>252</v>
       </c>
@@ -4437,7 +4734,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="84" spans="1:2">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>253</v>
       </c>
@@ -4445,7 +4742,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="85" spans="1:2">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>254</v>
       </c>
@@ -4453,7 +4750,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="86" spans="1:2">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>255</v>
       </c>
@@ -4461,7 +4758,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="87" spans="1:2">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>256</v>
       </c>
@@ -4469,7 +4766,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="88" spans="1:2">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>257</v>
       </c>
@@ -4477,7 +4774,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="89" spans="1:2">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>258</v>
       </c>
@@ -4485,7 +4782,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="90" spans="1:2">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>259</v>
       </c>
@@ -4493,7 +4790,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="91" spans="1:2">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>260</v>
       </c>
@@ -4501,7 +4798,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="92" spans="1:2">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>261</v>
       </c>
@@ -4509,7 +4806,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="93" spans="1:2">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>157</v>
       </c>
@@ -4517,7 +4814,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="94" spans="1:2">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>263</v>
       </c>
@@ -4525,7 +4822,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="95" spans="1:2">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>264</v>
       </c>
@@ -4533,7 +4830,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="96" spans="1:2">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>265</v>
       </c>
@@ -4541,7 +4838,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="97" spans="1:2">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" t="s">
         <v>266</v>
       </c>
@@ -4549,7 +4846,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="98" spans="1:2">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" t="s">
         <v>267</v>
       </c>
@@ -4557,7 +4854,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="99" spans="1:2">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" t="s">
         <v>268</v>
       </c>
@@ -4565,7 +4862,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="100" spans="1:2">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" t="s">
         <v>269</v>
       </c>
@@ -4573,7 +4870,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="101" spans="1:2">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" t="s">
         <v>270</v>
       </c>
@@ -4581,7 +4878,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="102" spans="1:2">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" t="s">
         <v>271</v>
       </c>
@@ -4589,7 +4886,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="103" spans="1:2">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" t="s">
         <v>272</v>
       </c>
@@ -4597,7 +4894,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="104" spans="1:2">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" t="s">
         <v>273</v>
       </c>
@@ -4605,7 +4902,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="105" spans="1:2">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" t="s">
         <v>274</v>
       </c>
@@ -4613,7 +4910,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="106" spans="1:2">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" t="s">
         <v>158</v>
       </c>
@@ -4621,7 +4918,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="107" spans="1:2">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" t="s">
         <v>275</v>
       </c>
@@ -4629,7 +4926,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="108" spans="1:2">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" t="s">
         <v>276</v>
       </c>
@@ -4637,7 +4934,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="109" spans="1:2">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" t="s">
         <v>277</v>
       </c>
@@ -4645,7 +4942,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="110" spans="1:2">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" t="s">
         <v>278</v>
       </c>
@@ -4653,7 +4950,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="111" spans="1:2">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" t="s">
         <v>279</v>
       </c>
@@ -4661,7 +4958,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="112" spans="1:2">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" t="s">
         <v>280</v>
       </c>
@@ -4669,7 +4966,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="113" spans="1:2">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" t="s">
         <v>281</v>
       </c>
@@ -4677,7 +4974,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="114" spans="1:2">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
         <v>282</v>
       </c>
@@ -4685,7 +4982,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="115" spans="1:2">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
         <v>283</v>
       </c>
@@ -4693,7 +4990,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="116" spans="1:2">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>284</v>
       </c>
@@ -4701,7 +4998,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="117" spans="1:2">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>285</v>
       </c>
@@ -4709,7 +5006,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="118" spans="1:2">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" t="s">
         <v>286</v>
       </c>
@@ -4717,7 +5014,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="119" spans="1:2">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
         <v>287</v>
       </c>
@@ -4725,7 +5022,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="120" spans="1:2">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
         <v>288</v>
       </c>
@@ -4733,7 +5030,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="121" spans="1:2">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>289</v>
       </c>
@@ -4741,7 +5038,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="122" spans="1:2">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>290</v>
       </c>
@@ -4749,7 +5046,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="123" spans="1:2">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>291</v>
       </c>
@@ -4757,7 +5054,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="124" spans="1:2">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>292</v>
       </c>
@@ -4765,7 +5062,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="125" spans="1:2">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>293</v>
       </c>
@@ -4773,7 +5070,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="126" spans="1:2">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" t="s">
         <v>294</v>
       </c>
@@ -4781,7 +5078,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="127" spans="1:2">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" t="s">
         <v>295</v>
       </c>
@@ -4789,7 +5086,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="128" spans="1:2">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" t="s">
         <v>296</v>
       </c>
@@ -4797,7 +5094,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="129" spans="1:2">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" t="s">
         <v>297</v>
       </c>
@@ -4805,7 +5102,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="130" spans="1:2">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" t="s">
         <v>298</v>
       </c>
@@ -4813,7 +5110,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="131" spans="1:2">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" t="s">
         <v>299</v>
       </c>
@@ -4821,7 +5118,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="132" spans="1:2">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" t="s">
         <v>300</v>
       </c>
@@ -4829,7 +5126,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="133" spans="1:2">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" t="s">
         <v>301</v>
       </c>
@@ -4837,7 +5134,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="134" spans="1:2">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" t="s">
         <v>302</v>
       </c>
@@ -4845,7 +5142,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="135" spans="1:2">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" t="s">
         <v>304</v>
       </c>
@@ -4853,7 +5150,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="136" spans="1:2">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" t="s">
         <v>305</v>
       </c>
@@ -4861,7 +5158,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="137" spans="1:2">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" t="s">
         <v>306</v>
       </c>
@@ -4869,7 +5166,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="138" spans="1:2">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" t="s">
         <v>307</v>
       </c>
@@ -4877,7 +5174,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="139" spans="1:2">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" t="s">
         <v>308</v>
       </c>
@@ -4885,7 +5182,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="140" spans="1:2">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" t="s">
         <v>309</v>
       </c>
@@ -4893,7 +5190,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="141" spans="1:2">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" t="s">
         <v>310</v>
       </c>
@@ -4901,7 +5198,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="142" spans="1:2">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" t="s">
         <v>311</v>
       </c>
@@ -4909,7 +5206,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="143" spans="1:2">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" t="s">
         <v>312</v>
       </c>
@@ -4917,7 +5214,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="144" spans="1:2">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" t="s">
         <v>313</v>
       </c>
@@ -4925,7 +5222,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="145" spans="1:2">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" t="s">
         <v>314</v>
       </c>
@@ -4933,7 +5230,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="146" spans="1:2">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" t="s">
         <v>315</v>
       </c>
@@ -4941,7 +5238,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="147" spans="1:2">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" t="s">
         <v>316</v>
       </c>
@@ -4949,7 +5246,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="148" spans="1:2">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" t="s">
         <v>317</v>
       </c>
@@ -4957,7 +5254,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="149" spans="1:2">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" t="s">
         <v>318</v>
       </c>
@@ -4965,7 +5262,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="150" spans="1:2">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" t="s">
         <v>319</v>
       </c>
@@ -4973,7 +5270,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="151" spans="1:2">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" t="s">
         <v>320</v>
       </c>
@@ -4981,7 +5278,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="152" spans="1:2">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" t="s">
         <v>321</v>
       </c>
@@ -4989,7 +5286,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:2">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" t="s">
         <v>322</v>
       </c>
@@ -4997,7 +5294,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="154" spans="1:2">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" t="s">
         <v>323</v>
       </c>
@@ -5005,7 +5302,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="155" spans="1:2">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" t="s">
         <v>324</v>
       </c>
@@ -5013,7 +5310,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="156" spans="1:2">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" t="s">
         <v>325</v>
       </c>
@@ -5021,7 +5318,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="157" spans="1:2">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" t="s">
         <v>326</v>
       </c>
@@ -5029,7 +5326,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="158" spans="1:2">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" t="s">
         <v>327</v>
       </c>
@@ -5037,7 +5334,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="159" spans="1:2">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" t="s">
         <v>328</v>
       </c>
@@ -5045,7 +5342,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="160" spans="1:2">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" t="s">
         <v>329</v>
       </c>
@@ -5053,7 +5350,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="161" spans="1:2">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" t="s">
         <v>330</v>
       </c>
@@ -5061,7 +5358,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="162" spans="1:2">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" t="s">
         <v>331</v>
       </c>
@@ -5069,7 +5366,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="163" spans="1:2">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" t="s">
         <v>332</v>
       </c>
@@ -5077,7 +5374,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="164" spans="1:2">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" t="s">
         <v>333</v>
       </c>
@@ -5085,7 +5382,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="165" spans="1:2">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" t="s">
         <v>334</v>
       </c>
@@ -5093,7 +5390,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="166" spans="1:2">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" t="s">
         <v>335</v>
       </c>
@@ -5101,7 +5398,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="167" spans="1:2">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" t="s">
         <v>336</v>
       </c>
@@ -5109,7 +5406,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="168" spans="1:2">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" t="s">
         <v>337</v>
       </c>
@@ -5117,7 +5414,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="169" spans="1:2">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" t="s">
         <v>338</v>
       </c>
@@ -5125,7 +5422,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="170" spans="1:2">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" t="s">
         <v>339</v>
       </c>
@@ -5133,7 +5430,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="171" spans="1:2">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" t="s">
         <v>340</v>
       </c>
@@ -5141,7 +5438,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="172" spans="1:2">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" t="s">
         <v>341</v>
       </c>
@@ -5149,7 +5446,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="173" spans="1:2">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" t="s">
         <v>342</v>
       </c>
@@ -5157,7 +5454,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="174" spans="1:2">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" t="s">
         <v>343</v>
       </c>
@@ -5165,7 +5462,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="175" spans="1:2">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" t="s">
         <v>344</v>
       </c>
@@ -5173,7 +5470,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="176" spans="1:2">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" t="s">
         <v>345</v>
       </c>
@@ -5181,7 +5478,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="177" spans="1:2">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" t="s">
         <v>346</v>
       </c>
@@ -5189,7 +5486,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="178" spans="1:2">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" t="s">
         <v>347</v>
       </c>
@@ -5197,7 +5494,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="179" spans="1:2">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" t="s">
         <v>348</v>
       </c>
@@ -5213,59 +5510,61 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:H154"/>
-  <sheetFormatPr defaultRowHeight="13"/>
+  <dimension ref="A1:H173"/>
+  <sheetFormatPr defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="51.81640625" style="17" customWidth="1"/>
-    <col min="2" max="2" width="35" style="17" customWidth="1"/>
-    <col min="3" max="5" width="28" style="17" customWidth="1"/>
-    <col min="6" max="6" width="14" style="17" customWidth="1"/>
-    <col min="7" max="7" width="10" style="17" customWidth="1"/>
-    <col min="8" max="8" width="12" style="17" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="17"/>
+    <col min="1" max="1" width="37.7265625" style="12" customWidth="1"/>
+    <col min="2" max="2" width="29.90625" style="12" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" style="12" customWidth="1"/>
+    <col min="4" max="4" width="18.26953125" style="12" customWidth="1"/>
+    <col min="5" max="5" width="22.6328125" style="12" customWidth="1"/>
+    <col min="6" max="6" width="14" style="12" customWidth="1"/>
+    <col min="7" max="7" width="10" style="12" customWidth="1"/>
+    <col min="8" max="8" width="12" style="12" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="18" customFormat="1" ht="28" customHeight="1">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" s="6" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="7" customFormat="1">
+    <row r="2" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A2" s="7" t="s">
+        <v>417</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>420</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>421</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>422</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>423</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>424</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>425</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>353</v>
@@ -5277,21 +5576,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="7" customFormat="1">
+    <row r="3" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A3" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>424</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>426</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>427</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>428</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>429</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>430</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>352</v>
@@ -5303,21 +5602,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="7" customFormat="1">
+    <row r="4" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A4" s="7" t="s">
+        <v>427</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>428</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>430</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>431</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>432</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>433</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>434</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>435</v>
       </c>
       <c r="F4" s="7" t="s">
         <v>352</v>
@@ -5329,21 +5628,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:8" s="7" customFormat="1">
+    <row r="5" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A5" s="7" t="s">
+        <v>432</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>433</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>434</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>435</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>436</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>437</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>438</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>439</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>440</v>
       </c>
       <c r="F5" s="7" t="s">
         <v>352</v>
@@ -5355,21 +5654,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:8" s="7" customFormat="1">
+    <row r="6" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A6" s="7" t="s">
+        <v>437</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>438</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>439</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>440</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>441</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>443</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>444</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>445</v>
       </c>
       <c r="F6" s="7" t="s">
         <v>353</v>
@@ -5381,24 +5680,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1">
+    <row r="7" spans="1:8" s="7" customFormat="1" ht="28" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="7" t="s">
+        <v>442</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>443</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>444</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>445</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>446</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="F7" s="7" t="s">
         <v>447</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>448</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>449</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>451</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>16</v>
@@ -5407,24 +5706,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="7" customFormat="1">
+    <row r="8" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A8" s="7" t="s">
+        <v>448</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>449</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>451</v>
+      </c>
+      <c r="E8" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>453</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>454</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>455</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>456</v>
-      </c>
       <c r="F8" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G8" s="8" t="s">
         <v>17</v>
@@ -5433,21 +5732,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:8" s="7" customFormat="1">
+    <row r="9" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A9" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>455</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>456</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>457</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>458</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>459</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>460</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>461</v>
       </c>
       <c r="F9" s="7" t="s">
         <v>355</v>
@@ -5459,21 +5758,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="7" customFormat="1">
+    <row r="10" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A10" s="7" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F10" s="7" t="s">
         <v>355</v>
@@ -5485,21 +5784,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:8" s="7" customFormat="1">
+    <row r="11" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A11" s="7" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="F11" s="7" t="s">
         <v>353</v>
@@ -5511,21 +5810,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:8" s="7" customFormat="1" ht="36" customHeight="1">
+    <row r="12" spans="1:8" s="7" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>461</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>462</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>463</v>
+      </c>
+      <c r="E12" s="7" t="s">
         <v>464</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>465</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>466</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>468</v>
       </c>
       <c r="F12" s="7" t="s">
         <v>355</v>
@@ -5537,24 +5836,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:8" s="7" customFormat="1">
+    <row r="13" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A13" s="7" t="s">
+        <v>465</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>466</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="E13" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B13" s="7" t="s">
-        <v>470</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>471</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>473</v>
-      </c>
       <c r="F13" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G13" s="9" t="s">
         <v>22</v>
@@ -5563,21 +5862,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:8" s="7" customFormat="1">
+    <row r="14" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A14" s="7" t="s">
+        <v>470</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>472</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>473</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>474</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>475</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>476</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>477</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>478</v>
       </c>
       <c r="F14" s="7" t="s">
         <v>353</v>
@@ -5589,21 +5888,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:8" s="7" customFormat="1">
+    <row r="15" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A15" s="7" t="s">
+        <v>475</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>476</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>477</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>478</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>479</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>480</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>481</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>482</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>483</v>
       </c>
       <c r="F15" s="7" t="s">
         <v>352</v>
@@ -5615,21 +5914,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:8" s="7" customFormat="1">
+    <row r="16" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A16" s="7" t="s">
+        <v>480</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>481</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>482</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>483</v>
+      </c>
+      <c r="E16" s="7" t="s">
         <v>484</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>485</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>486</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>487</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>488</v>
       </c>
       <c r="F16" s="7" t="s">
         <v>353</v>
@@ -5641,21 +5940,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:8" s="7" customFormat="1">
+    <row r="17" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A17" s="7" t="s">
+        <v>485</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>486</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>487</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>488</v>
+      </c>
+      <c r="E17" s="7" t="s">
         <v>489</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>490</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>491</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>492</v>
-      </c>
-      <c r="E17" s="7" t="s">
-        <v>493</v>
       </c>
       <c r="F17" s="7" t="s">
         <v>353</v>
@@ -5667,21 +5966,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="7" customFormat="1">
+    <row r="18" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A18" s="7" t="s">
+        <v>490</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>491</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>492</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>493</v>
+      </c>
+      <c r="E18" s="7" t="s">
         <v>494</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>495</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>496</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>497</v>
-      </c>
-      <c r="E18" s="7" t="s">
-        <v>498</v>
       </c>
       <c r="F18" s="7" t="s">
         <v>355</v>
@@ -5693,24 +5992,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:8" s="7" customFormat="1">
+    <row r="19" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A19" s="7" t="s">
+        <v>495</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>496</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>497</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>498</v>
+      </c>
+      <c r="E19" s="7" t="s">
         <v>499</v>
       </c>
-      <c r="B19" s="7" t="s">
-        <v>500</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>502</v>
-      </c>
-      <c r="E19" s="7" t="s">
-        <v>503</v>
-      </c>
       <c r="F19" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G19" s="9" t="s">
         <v>28</v>
@@ -5719,21 +6018,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:8" s="7" customFormat="1">
+    <row r="20" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A20" s="7" t="s">
+        <v>500</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>501</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>502</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>503</v>
+      </c>
+      <c r="E20" s="7" t="s">
         <v>504</v>
-      </c>
-      <c r="B20" s="7" t="s">
-        <v>505</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>506</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>507</v>
-      </c>
-      <c r="E20" s="7" t="s">
-        <v>508</v>
       </c>
       <c r="F20" s="7" t="s">
         <v>353</v>
@@ -5745,21 +6044,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="7" customFormat="1">
+    <row r="21" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A21" s="7" t="s">
+        <v>505</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>506</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>507</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>508</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>509</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>510</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>511</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>512</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>513</v>
       </c>
       <c r="F21" s="7" t="s">
         <v>353</v>
@@ -5771,21 +6070,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="7" customFormat="1">
+    <row r="22" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A22" s="7" t="s">
+        <v>510</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>511</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>512</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>513</v>
+      </c>
+      <c r="E22" s="7" t="s">
         <v>514</v>
-      </c>
-      <c r="B22" s="7" t="s">
-        <v>515</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>516</v>
-      </c>
-      <c r="D22" s="7" t="s">
-        <v>517</v>
-      </c>
-      <c r="E22" s="7" t="s">
-        <v>518</v>
       </c>
       <c r="F22" s="7" t="s">
         <v>352</v>
@@ -5797,21 +6096,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="7" customFormat="1">
+    <row r="23" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A23" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>516</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>517</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>518</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>519</v>
-      </c>
-      <c r="B23" s="7" t="s">
-        <v>520</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>522</v>
-      </c>
-      <c r="E23" s="7" t="s">
-        <v>523</v>
       </c>
       <c r="F23" s="7" t="s">
         <v>352</v>
@@ -5823,24 +6122,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="7" customFormat="1">
+    <row r="24" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A24" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="B24" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>522</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>523</v>
+      </c>
+      <c r="E24" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>526</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>527</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>528</v>
-      </c>
       <c r="F24" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G24" s="8" t="s">
         <v>33</v>
@@ -5849,21 +6148,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:8" s="7" customFormat="1">
+    <row r="25" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A25" s="7" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="F25" s="7" t="s">
         <v>353</v>
@@ -5875,21 +6174,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="7" customFormat="1">
+    <row r="26" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A26" s="7" t="s">
+        <v>529</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>530</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>531</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>532</v>
+      </c>
+      <c r="E26" s="7" t="s">
         <v>533</v>
-      </c>
-      <c r="B26" s="7" t="s">
-        <v>534</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>535</v>
-      </c>
-      <c r="D26" s="7" t="s">
-        <v>536</v>
-      </c>
-      <c r="E26" s="7" t="s">
-        <v>537</v>
       </c>
       <c r="F26" s="7" t="s">
         <v>352</v>
@@ -5901,24 +6200,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" s="7" customFormat="1">
+    <row r="27" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A27" s="7" t="s">
+        <v>534</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>535</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>536</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>537</v>
+      </c>
+      <c r="E27" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>539</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>540</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>541</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>542</v>
-      </c>
       <c r="F27" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G27" s="9" t="s">
         <v>36</v>
@@ -5927,21 +6226,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:8" s="7" customFormat="1">
+    <row r="28" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A28" s="7" t="s">
+        <v>539</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>540</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>541</v>
+      </c>
+      <c r="D28" s="7" t="s">
+        <v>542</v>
+      </c>
+      <c r="E28" s="7" t="s">
         <v>543</v>
-      </c>
-      <c r="B28" s="7" t="s">
-        <v>544</v>
-      </c>
-      <c r="C28" s="7" t="s">
-        <v>545</v>
-      </c>
-      <c r="D28" s="7" t="s">
-        <v>546</v>
-      </c>
-      <c r="E28" s="7" t="s">
-        <v>547</v>
       </c>
       <c r="F28" s="7" t="s">
         <v>352</v>
@@ -5953,21 +6252,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:8" s="7" customFormat="1">
+    <row r="29" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A29" s="7" t="s">
+        <v>544</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>545</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>546</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>547</v>
+      </c>
+      <c r="E29" s="7" t="s">
         <v>548</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>549</v>
-      </c>
-      <c r="C29" s="7" t="s">
-        <v>550</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>551</v>
-      </c>
-      <c r="E29" s="7" t="s">
-        <v>552</v>
       </c>
       <c r="F29" s="7" t="s">
         <v>353</v>
@@ -5979,21 +6278,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:8" s="7" customFormat="1">
+    <row r="30" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A30" s="7" t="s">
+        <v>549</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>550</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>551</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>552</v>
+      </c>
+      <c r="E30" s="7" t="s">
         <v>553</v>
-      </c>
-      <c r="B30" s="7" t="s">
-        <v>554</v>
-      </c>
-      <c r="C30" s="7" t="s">
-        <v>555</v>
-      </c>
-      <c r="D30" s="7" t="s">
-        <v>556</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>557</v>
       </c>
       <c r="F30" s="7" t="s">
         <v>352</v>
@@ -6005,21 +6304,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="31" spans="1:8" s="7" customFormat="1">
+    <row r="31" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A31" s="7" t="s">
+        <v>554</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>555</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>556</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>557</v>
+      </c>
+      <c r="E31" s="7" t="s">
         <v>558</v>
-      </c>
-      <c r="B31" s="7" t="s">
-        <v>559</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>560</v>
-      </c>
-      <c r="D31" s="7" t="s">
-        <v>561</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>562</v>
       </c>
       <c r="F31" s="7" t="s">
         <v>352</v>
@@ -6031,21 +6330,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:8" s="7" customFormat="1">
+    <row r="32" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A32" s="7" t="s">
+        <v>559</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>560</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>561</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>562</v>
+      </c>
+      <c r="E32" s="7" t="s">
         <v>563</v>
-      </c>
-      <c r="B32" s="7" t="s">
-        <v>564</v>
-      </c>
-      <c r="C32" s="7" t="s">
-        <v>565</v>
-      </c>
-      <c r="D32" s="7" t="s">
-        <v>566</v>
-      </c>
-      <c r="E32" s="7" t="s">
-        <v>567</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>353</v>
@@ -6057,21 +6356,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:8" s="7" customFormat="1">
+    <row r="33" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A33" s="7" t="s">
+        <v>564</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>565</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>566</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="E33" s="7" t="s">
         <v>568</v>
-      </c>
-      <c r="B33" s="7" t="s">
-        <v>569</v>
-      </c>
-      <c r="C33" s="7" t="s">
-        <v>570</v>
-      </c>
-      <c r="D33" s="7" t="s">
-        <v>571</v>
-      </c>
-      <c r="E33" s="7" t="s">
-        <v>572</v>
       </c>
       <c r="F33" s="7" t="s">
         <v>353</v>
@@ -6083,21 +6382,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:8" s="7" customFormat="1" ht="24.5" customHeight="1">
+    <row r="34" spans="1:8" s="7" customFormat="1" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="7" t="s">
-        <v>573</v>
+        <v>569</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>574</v>
+        <v>570</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="F34" s="7" t="s">
         <v>355</v>
@@ -6109,21 +6408,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:8" s="7" customFormat="1">
+    <row r="35" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A35" s="7" t="s">
-        <v>576</v>
+        <v>572</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>577</v>
+        <v>573</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>578</v>
+        <v>574</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>572</v>
+        <v>568</v>
       </c>
       <c r="E35" s="7" t="s">
-        <v>579</v>
+        <v>575</v>
       </c>
       <c r="F35" s="7" t="s">
         <v>352</v>
@@ -6135,21 +6434,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:8" s="7" customFormat="1" ht="26.5" customHeight="1">
+    <row r="36" spans="1:8" s="7" customFormat="1" ht="26.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="7" t="s">
         <v>360</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>580</v>
+        <v>576</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>581</v>
+        <v>577</v>
       </c>
       <c r="D36" s="7" t="s">
-        <v>582</v>
+        <v>578</v>
       </c>
       <c r="E36" s="7" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="F36" s="7" t="s">
         <v>352</v>
@@ -6161,21 +6460,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:8" s="7" customFormat="1">
+    <row r="37" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A37" s="7" t="s">
+        <v>580</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>581</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>582</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>583</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>584</v>
-      </c>
-      <c r="B37" s="7" t="s">
-        <v>585</v>
-      </c>
-      <c r="C37" s="7" t="s">
-        <v>586</v>
-      </c>
-      <c r="D37" s="7" t="s">
-        <v>587</v>
-      </c>
-      <c r="E37" s="7" t="s">
-        <v>588</v>
       </c>
       <c r="F37" s="7" t="s">
         <v>352</v>
@@ -6187,21 +6486,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:8" s="7" customFormat="1">
+    <row r="38" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A38" s="7" t="s">
+        <v>585</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>586</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>587</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>588</v>
+      </c>
+      <c r="E38" s="7" t="s">
         <v>589</v>
-      </c>
-      <c r="B38" s="7" t="s">
-        <v>590</v>
-      </c>
-      <c r="C38" s="7" t="s">
-        <v>591</v>
-      </c>
-      <c r="D38" s="7" t="s">
-        <v>592</v>
-      </c>
-      <c r="E38" s="7" t="s">
-        <v>593</v>
       </c>
       <c r="F38" s="7" t="s">
         <v>355</v>
@@ -6213,18 +6512,18 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:8" s="7" customFormat="1">
+    <row r="39" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A39" s="7" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="B39" s="7" t="s">
         <v>358</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="E39" s="7" t="s">
         <v>359</v>
@@ -6239,21 +6538,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:8" s="7" customFormat="1">
+    <row r="40" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A40" s="7" t="s">
+        <v>593</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>594</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>595</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>596</v>
+      </c>
+      <c r="E40" s="7" t="s">
         <v>597</v>
-      </c>
-      <c r="B40" s="7" t="s">
-        <v>598</v>
-      </c>
-      <c r="C40" s="7" t="s">
-        <v>599</v>
-      </c>
-      <c r="D40" s="7" t="s">
-        <v>600</v>
-      </c>
-      <c r="E40" s="7" t="s">
-        <v>601</v>
       </c>
       <c r="F40" s="7" t="s">
         <v>352</v>
@@ -6265,21 +6564,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:8" s="7" customFormat="1">
+    <row r="41" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A41" s="7" t="s">
+        <v>598</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>599</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>600</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>601</v>
+      </c>
+      <c r="E41" s="7" t="s">
         <v>602</v>
-      </c>
-      <c r="B41" s="7" t="s">
-        <v>603</v>
-      </c>
-      <c r="C41" s="7" t="s">
-        <v>604</v>
-      </c>
-      <c r="D41" s="7" t="s">
-        <v>605</v>
-      </c>
-      <c r="E41" s="7" t="s">
-        <v>606</v>
       </c>
       <c r="F41" s="7" t="s">
         <v>352</v>
@@ -6291,21 +6590,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:8" s="7" customFormat="1">
+    <row r="42" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A42" s="7" t="s">
+        <v>603</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>604</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>605</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>606</v>
+      </c>
+      <c r="E42" s="7" t="s">
         <v>607</v>
-      </c>
-      <c r="B42" s="7" t="s">
-        <v>608</v>
-      </c>
-      <c r="C42" s="7" t="s">
-        <v>609</v>
-      </c>
-      <c r="D42" s="7" t="s">
-        <v>610</v>
-      </c>
-      <c r="E42" s="7" t="s">
-        <v>611</v>
       </c>
       <c r="F42" s="7" t="s">
         <v>353</v>
@@ -6317,21 +6616,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:8" s="7" customFormat="1">
+    <row r="43" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A43" s="7" t="s">
+        <v>608</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>609</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>610</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>611</v>
+      </c>
+      <c r="E43" s="7" t="s">
         <v>612</v>
-      </c>
-      <c r="B43" s="7" t="s">
-        <v>613</v>
-      </c>
-      <c r="C43" s="7" t="s">
-        <v>614</v>
-      </c>
-      <c r="D43" s="7" t="s">
-        <v>615</v>
-      </c>
-      <c r="E43" s="7" t="s">
-        <v>616</v>
       </c>
       <c r="F43" s="7" t="s">
         <v>353</v>
@@ -6343,21 +6642,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:8" s="7" customFormat="1">
+    <row r="44" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A44" s="7" t="s">
-        <v>617</v>
+        <v>613</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D44" s="7" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="E44" s="7" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="F44" s="7" t="s">
         <v>353</v>
@@ -6369,24 +6668,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:8" s="7" customFormat="1">
+    <row r="45" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A45" s="7" t="s">
+        <v>614</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>615</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>616</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>617</v>
+      </c>
+      <c r="E45" s="7" t="s">
         <v>618</v>
       </c>
-      <c r="B45" s="7" t="s">
-        <v>619</v>
-      </c>
-      <c r="C45" s="7" t="s">
-        <v>620</v>
-      </c>
-      <c r="D45" s="7" t="s">
-        <v>621</v>
-      </c>
-      <c r="E45" s="7" t="s">
-        <v>622</v>
-      </c>
       <c r="F45" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G45" s="9" t="s">
         <v>54</v>
@@ -6395,21 +6694,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:8" s="7" customFormat="1">
+    <row r="46" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A46" s="7" t="s">
-        <v>623</v>
+        <v>619</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="D46" s="7" t="s">
-        <v>999</v>
+        <v>995</v>
       </c>
       <c r="E46" s="7" t="s">
-        <v>1000</v>
+        <v>996</v>
       </c>
       <c r="F46" s="7" t="s">
         <v>353</v>
@@ -6421,21 +6720,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:8" s="7" customFormat="1">
+    <row r="47" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A47" s="7" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>1001</v>
+        <v>997</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>1002</v>
+        <v>998</v>
       </c>
       <c r="D47" s="7" t="s">
-        <v>1003</v>
+        <v>999</v>
       </c>
       <c r="E47" s="7" t="s">
-        <v>1004</v>
+        <v>1000</v>
       </c>
       <c r="F47" s="7" t="s">
         <v>352</v>
@@ -6447,21 +6746,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:8" s="7" customFormat="1">
+    <row r="48" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A48" s="7" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>1005</v>
+        <v>1001</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>1006</v>
+        <v>1002</v>
       </c>
       <c r="D48" s="7" t="s">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>1008</v>
+        <v>1004</v>
       </c>
       <c r="F48" s="7" t="s">
         <v>355</v>
@@ -6473,24 +6772,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:8" s="7" customFormat="1">
+    <row r="49" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A49" s="7" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>1009</v>
+        <v>1005</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>1010</v>
+        <v>1006</v>
       </c>
       <c r="D49" s="7" t="s">
-        <v>1011</v>
+        <v>1007</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>1012</v>
+        <v>1008</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G49" s="9" t="s">
         <v>58</v>
@@ -6499,21 +6798,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:8" s="7" customFormat="1">
+    <row r="50" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A50" s="7" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>1013</v>
+        <v>1009</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="D50" s="7" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>1016</v>
+        <v>1012</v>
       </c>
       <c r="F50" s="7" t="s">
         <v>355</v>
@@ -6525,21 +6824,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:8" s="7" customFormat="1">
+    <row r="51" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A51" s="7" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="B51" s="7" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="D51" s="7" t="s">
-        <v>1019</v>
+        <v>1015</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="F51" s="7" t="s">
         <v>353</v>
@@ -6551,21 +6850,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:8" s="7" customFormat="1">
+    <row r="52" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="7" t="s">
-        <v>629</v>
+        <v>625</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>1022</v>
+        <v>1018</v>
       </c>
       <c r="D52" s="7" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="E52" s="7" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="F52" s="7" t="s">
         <v>353</v>
@@ -6577,24 +6876,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="7" customFormat="1">
+    <row r="53" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="7" t="s">
-        <v>630</v>
+        <v>626</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>631</v>
+        <v>627</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>1025</v>
+        <v>1021</v>
       </c>
       <c r="D53" s="7" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="E53" s="7" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="F53" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G53" s="9" t="s">
         <v>62</v>
@@ -6603,21 +6902,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:8" s="7" customFormat="1">
+    <row r="54" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A54" s="7" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B54" s="7" t="s">
-        <v>1028</v>
+        <v>1024</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="D54" s="7" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="E54" s="7" t="s">
-        <v>1031</v>
+        <v>1027</v>
       </c>
       <c r="F54" s="7" t="s">
         <v>352</v>
@@ -6629,21 +6928,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:8" s="7" customFormat="1">
+    <row r="55" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="7" t="s">
-        <v>632</v>
+        <v>628</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="D55" s="7" t="s">
-        <v>1034</v>
+        <v>1030</v>
       </c>
       <c r="E55" s="7" t="s">
-        <v>1035</v>
+        <v>1031</v>
       </c>
       <c r="F55" s="7" t="s">
         <v>355</v>
@@ -6655,21 +6954,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:8" s="7" customFormat="1">
+    <row r="56" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="7" t="s">
-        <v>633</v>
+        <v>629</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>1036</v>
+        <v>1032</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>1037</v>
+        <v>1033</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>1038</v>
+        <v>1034</v>
       </c>
       <c r="E56" s="7" t="s">
-        <v>1039</v>
+        <v>1035</v>
       </c>
       <c r="F56" s="7" t="s">
         <v>353</v>
@@ -6681,21 +6980,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:8" s="7" customFormat="1">
+    <row r="57" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A57" s="7" t="s">
-        <v>634</v>
+        <v>630</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>1040</v>
+        <v>1036</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="E57" s="7" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="F57" s="7" t="s">
         <v>353</v>
@@ -6707,21 +7006,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:8" s="7" customFormat="1">
+    <row r="58" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A58" s="7" t="s">
+        <v>631</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>632</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="E58" s="7" t="s">
         <v>635</v>
-      </c>
-      <c r="B58" s="7" t="s">
-        <v>636</v>
-      </c>
-      <c r="C58" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="D58" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="E58" s="7" t="s">
-        <v>639</v>
       </c>
       <c r="F58" s="7" t="s">
         <v>355</v>
@@ -6733,21 +7032,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:8" s="7" customFormat="1">
+    <row r="59" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A59" s="7" t="s">
-        <v>640</v>
+        <v>636</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="D59" s="7" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E59" s="7" t="s">
-        <v>639</v>
+        <v>635</v>
       </c>
       <c r="F59" s="7" t="s">
         <v>355</v>
@@ -6759,24 +7058,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:8" s="7" customFormat="1">
+    <row r="60" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A60" s="7" t="s">
-        <v>641</v>
+        <v>637</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>1047</v>
+        <v>1043</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G60" s="8" t="s">
         <v>69</v>
@@ -6785,21 +7084,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:8" s="7" customFormat="1">
+    <row r="61" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A61" s="7" t="s">
-        <v>642</v>
+        <v>638</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="F61" s="7" t="s">
         <v>352</v>
@@ -6811,21 +7110,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:8" s="7" customFormat="1" ht="26">
-      <c r="A62" s="10" t="s">
-        <v>643</v>
-      </c>
-      <c r="B62" s="11" t="s">
-        <v>1052</v>
-      </c>
-      <c r="C62" s="11" t="s">
-        <v>1053</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>1054</v>
-      </c>
-      <c r="E62" s="11" t="s">
-        <v>1055</v>
+    <row r="62" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A62" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C62" s="14" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D62" s="14" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E62" s="14" t="s">
+        <v>1051</v>
       </c>
       <c r="F62" s="8" t="s">
         <v>352</v>
@@ -6837,21 +7136,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="7" customFormat="1">
-      <c r="A63" s="12" t="s">
+    <row r="63" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A63" s="10" t="s">
+        <v>640</v>
+      </c>
+      <c r="B63" s="10" t="s">
+        <v>641</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>642</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>643</v>
+      </c>
+      <c r="E63" s="10" t="s">
         <v>644</v>
-      </c>
-      <c r="B63" s="12" t="s">
-        <v>645</v>
-      </c>
-      <c r="C63" s="12" t="s">
-        <v>646</v>
-      </c>
-      <c r="D63" s="12" t="s">
-        <v>647</v>
-      </c>
-      <c r="E63" s="13" t="s">
-        <v>648</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>355</v>
@@ -6863,21 +7162,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:8" s="7" customFormat="1">
-      <c r="A64" s="12" t="s">
-        <v>649</v>
-      </c>
-      <c r="B64" s="12" t="s">
-        <v>1056</v>
-      </c>
-      <c r="C64" s="12" t="s">
-        <v>1057</v>
-      </c>
-      <c r="D64" s="12" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E64" s="12" t="s">
-        <v>1059</v>
+    <row r="64" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A64" s="10" t="s">
+        <v>645</v>
+      </c>
+      <c r="B64" s="10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>1053</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>1054</v>
+      </c>
+      <c r="E64" s="10" t="s">
+        <v>1055</v>
       </c>
       <c r="F64" s="8" t="s">
         <v>352</v>
@@ -6889,24 +7188,24 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:8" s="7" customFormat="1">
-      <c r="A65" s="12" t="s">
-        <v>650</v>
-      </c>
-      <c r="B65" s="12" t="s">
+    <row r="65" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="10" t="s">
+        <v>646</v>
+      </c>
+      <c r="B65" s="10" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C65" s="10" t="s">
         <v>1056</v>
       </c>
-      <c r="C65" s="12" t="s">
-        <v>1060</v>
-      </c>
-      <c r="D65" s="12" t="s">
-        <v>1061</v>
-      </c>
-      <c r="E65" s="12" t="s">
-        <v>1062</v>
+      <c r="D65" s="10" t="s">
+        <v>1057</v>
+      </c>
+      <c r="E65" s="10" t="s">
+        <v>1058</v>
       </c>
       <c r="F65" s="9" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G65" s="9" t="s">
         <v>74</v>
@@ -6915,21 +7214,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:8" s="7" customFormat="1">
-      <c r="A66" s="12" t="s">
-        <v>651</v>
-      </c>
-      <c r="B66" s="12" t="s">
-        <v>1063</v>
-      </c>
-      <c r="C66" s="12" t="s">
-        <v>1064</v>
-      </c>
-      <c r="D66" s="12" t="s">
-        <v>1065</v>
-      </c>
-      <c r="E66" s="12" t="s">
-        <v>1066</v>
+    <row r="66" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="10" t="s">
+        <v>647</v>
+      </c>
+      <c r="B66" s="10" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>1061</v>
+      </c>
+      <c r="E66" s="10" t="s">
+        <v>1062</v>
       </c>
       <c r="F66" s="8" t="s">
         <v>355</v>
@@ -6941,21 +7240,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:8" s="7" customFormat="1">
-      <c r="A67" s="12" t="s">
+    <row r="67" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="10" t="s">
+        <v>648</v>
+      </c>
+      <c r="B67" s="10" t="s">
+        <v>649</v>
+      </c>
+      <c r="C67" s="10" t="s">
+        <v>650</v>
+      </c>
+      <c r="D67" s="10" t="s">
+        <v>651</v>
+      </c>
+      <c r="E67" s="10" t="s">
         <v>652</v>
-      </c>
-      <c r="B67" s="12" t="s">
-        <v>653</v>
-      </c>
-      <c r="C67" s="12" t="s">
-        <v>654</v>
-      </c>
-      <c r="D67" s="12" t="s">
-        <v>655</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>656</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>352</v>
@@ -6967,21 +7266,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:8" s="7" customFormat="1">
-      <c r="A68" s="12" t="s">
+    <row r="68" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="10" t="s">
+        <v>653</v>
+      </c>
+      <c r="B68" s="8" t="s">
+        <v>654</v>
+      </c>
+      <c r="C68" s="8" t="s">
+        <v>655</v>
+      </c>
+      <c r="D68" s="8" t="s">
+        <v>656</v>
+      </c>
+      <c r="E68" s="8" t="s">
         <v>657</v>
-      </c>
-      <c r="B68" s="8" t="s">
-        <v>658</v>
-      </c>
-      <c r="C68" s="8" t="s">
-        <v>659</v>
-      </c>
-      <c r="D68" s="8" t="s">
-        <v>660</v>
-      </c>
-      <c r="E68" s="8" t="s">
-        <v>661</v>
       </c>
       <c r="F68" s="8" t="s">
         <v>355</v>
@@ -6993,21 +7292,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:8" s="7" customFormat="1">
-      <c r="A69" s="12" t="s">
+    <row r="69" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="10" t="s">
+        <v>658</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>659</v>
+      </c>
+      <c r="C69" s="9" t="s">
+        <v>660</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>661</v>
+      </c>
+      <c r="E69" s="9" t="s">
         <v>662</v>
-      </c>
-      <c r="B69" s="9" t="s">
-        <v>663</v>
-      </c>
-      <c r="C69" s="9" t="s">
-        <v>664</v>
-      </c>
-      <c r="D69" s="9" t="s">
-        <v>665</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>666</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>352</v>
@@ -7019,21 +7318,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:8" s="7" customFormat="1">
-      <c r="A70" s="12" t="s">
+    <row r="70" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A70" s="10" t="s">
+        <v>663</v>
+      </c>
+      <c r="B70" s="8" t="s">
+        <v>664</v>
+      </c>
+      <c r="C70" s="8" t="s">
+        <v>665</v>
+      </c>
+      <c r="D70" s="8" t="s">
+        <v>666</v>
+      </c>
+      <c r="E70" s="8" t="s">
         <v>667</v>
-      </c>
-      <c r="B70" s="8" t="s">
-        <v>668</v>
-      </c>
-      <c r="C70" s="8" t="s">
-        <v>669</v>
-      </c>
-      <c r="D70" s="8" t="s">
-        <v>670</v>
-      </c>
-      <c r="E70" s="8" t="s">
-        <v>671</v>
       </c>
       <c r="F70" s="8" t="s">
         <v>353</v>
@@ -7045,21 +7344,21 @@
         <v>11</v>
       </c>
     </row>
-    <row r="71" spans="1:8" s="7" customFormat="1">
-      <c r="A71" s="12" t="s">
+    <row r="71" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="10" t="s">
+        <v>668</v>
+      </c>
+      <c r="B71" s="9" t="s">
+        <v>669</v>
+      </c>
+      <c r="C71" s="9" t="s">
+        <v>670</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>671</v>
+      </c>
+      <c r="E71" s="9" t="s">
         <v>672</v>
-      </c>
-      <c r="B71" s="9" t="s">
-        <v>673</v>
-      </c>
-      <c r="C71" s="9" t="s">
-        <v>674</v>
-      </c>
-      <c r="D71" s="9" t="s">
-        <v>675</v>
-      </c>
-      <c r="E71" s="9" t="s">
-        <v>676</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>353</v>
@@ -7071,47 +7370,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:8" s="7" customFormat="1">
+    <row r="72" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A72" s="9" t="s">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="C72" s="9" t="s">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="D72" s="7" t="s">
-        <v>679</v>
+        <v>675</v>
       </c>
       <c r="E72" s="7" t="s">
-        <v>680</v>
+        <v>676</v>
       </c>
       <c r="F72" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="G72" s="9" t="s">
+      <c r="G72" s="8" t="s">
         <v>81</v>
       </c>
       <c r="H72" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="7" customFormat="1">
-      <c r="A73" s="12" t="s">
+    <row r="73" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A73" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B73" s="11" t="s">
+        <v>678</v>
+      </c>
+      <c r="C73" s="9" t="s">
+        <v>679</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>680</v>
+      </c>
+      <c r="E73" s="9" t="s">
         <v>681</v>
-      </c>
-      <c r="B73" s="14" t="s">
-        <v>682</v>
-      </c>
-      <c r="C73" s="9" t="s">
-        <v>683</v>
-      </c>
-      <c r="D73" s="9" t="s">
-        <v>684</v>
-      </c>
-      <c r="E73" s="9" t="s">
-        <v>685</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>355</v>
@@ -7123,47 +7422,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:8" s="7" customFormat="1">
-      <c r="A74" s="12" t="s">
+    <row r="74" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="10" t="s">
+        <v>682</v>
+      </c>
+      <c r="B74" s="11" t="s">
+        <v>683</v>
+      </c>
+      <c r="C74" s="9" t="s">
+        <v>684</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>685</v>
+      </c>
+      <c r="E74" s="9" t="s">
         <v>686</v>
-      </c>
-      <c r="B74" s="14" t="s">
-        <v>687</v>
-      </c>
-      <c r="C74" s="9" t="s">
-        <v>688</v>
-      </c>
-      <c r="D74" s="9" t="s">
-        <v>689</v>
-      </c>
-      <c r="E74" s="9" t="s">
-        <v>690</v>
       </c>
       <c r="F74" s="9" t="s">
         <v>352</v>
       </c>
-      <c r="G74" s="9" t="s">
+      <c r="G74" s="8" t="s">
         <v>83</v>
       </c>
       <c r="H74" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:8" s="7" customFormat="1">
-      <c r="A75" s="12" t="s">
+    <row r="75" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A75" s="10" t="s">
+        <v>687</v>
+      </c>
+      <c r="B75" s="11" t="s">
+        <v>688</v>
+      </c>
+      <c r="C75" s="9" t="s">
+        <v>689</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>690</v>
+      </c>
+      <c r="E75" s="9" t="s">
         <v>691</v>
-      </c>
-      <c r="B75" s="14" t="s">
-        <v>692</v>
-      </c>
-      <c r="C75" s="9" t="s">
-        <v>693</v>
-      </c>
-      <c r="D75" s="9" t="s">
-        <v>694</v>
-      </c>
-      <c r="E75" s="9" t="s">
-        <v>695</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>352</v>
@@ -7175,50 +7474,50 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:8" s="7" customFormat="1">
-      <c r="A76" s="12" t="s">
+    <row r="76" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A76" s="10" t="s">
+        <v>692</v>
+      </c>
+      <c r="B76" s="11" t="s">
+        <v>693</v>
+      </c>
+      <c r="C76" s="9" t="s">
+        <v>694</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>695</v>
+      </c>
+      <c r="E76" s="9" t="s">
         <v>696</v>
-      </c>
-      <c r="B76" s="14" t="s">
-        <v>697</v>
-      </c>
-      <c r="C76" s="9" t="s">
-        <v>698</v>
-      </c>
-      <c r="D76" s="9" t="s">
-        <v>699</v>
-      </c>
-      <c r="E76" s="9" t="s">
-        <v>700</v>
       </c>
       <c r="F76" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="G76" s="9" t="s">
+      <c r="G76" s="8" t="s">
         <v>85</v>
       </c>
       <c r="H76" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:8" s="7" customFormat="1">
-      <c r="A77" s="12" t="s">
+    <row r="77" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A77" s="10" t="s">
+        <v>697</v>
+      </c>
+      <c r="B77" s="11" t="s">
+        <v>698</v>
+      </c>
+      <c r="C77" s="9" t="s">
+        <v>699</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>700</v>
+      </c>
+      <c r="E77" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="B77" s="14" t="s">
-        <v>702</v>
-      </c>
-      <c r="C77" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="D77" s="9" t="s">
-        <v>704</v>
-      </c>
-      <c r="E77" s="9" t="s">
-        <v>705</v>
-      </c>
       <c r="F77" s="9" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G77" s="9" t="s">
         <v>86</v>
@@ -7227,47 +7526,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="78" spans="1:8" s="7" customFormat="1">
-      <c r="A78" s="12" t="s">
+    <row r="78" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="10" t="s">
+        <v>702</v>
+      </c>
+      <c r="B78" s="11" t="s">
+        <v>703</v>
+      </c>
+      <c r="C78" s="9" t="s">
+        <v>704</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>705</v>
+      </c>
+      <c r="E78" s="9" t="s">
         <v>706</v>
-      </c>
-      <c r="B78" s="14" t="s">
-        <v>707</v>
-      </c>
-      <c r="C78" s="9" t="s">
-        <v>708</v>
-      </c>
-      <c r="D78" s="9" t="s">
-        <v>709</v>
-      </c>
-      <c r="E78" s="9" t="s">
-        <v>710</v>
       </c>
       <c r="F78" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="G78" s="9" t="s">
+      <c r="G78" s="8" t="s">
         <v>87</v>
       </c>
       <c r="H78" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="79" spans="1:8" s="7" customFormat="1">
-      <c r="A79" s="12" t="s">
+    <row r="79" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="10" t="s">
+        <v>707</v>
+      </c>
+      <c r="B79" s="11" t="s">
+        <v>708</v>
+      </c>
+      <c r="C79" s="9" t="s">
+        <v>709</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>710</v>
+      </c>
+      <c r="E79" s="9" t="s">
         <v>711</v>
-      </c>
-      <c r="B79" s="14" t="s">
-        <v>712</v>
-      </c>
-      <c r="C79" s="9" t="s">
-        <v>713</v>
-      </c>
-      <c r="D79" s="9" t="s">
-        <v>714</v>
-      </c>
-      <c r="E79" s="9" t="s">
-        <v>715</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>352</v>
@@ -7279,47 +7578,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="80" spans="1:8" s="7" customFormat="1">
-      <c r="A80" s="12" t="s">
+    <row r="80" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A80" s="10" t="s">
+        <v>712</v>
+      </c>
+      <c r="B80" s="11" t="s">
+        <v>713</v>
+      </c>
+      <c r="C80" s="9" t="s">
+        <v>714</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>715</v>
+      </c>
+      <c r="E80" s="9" t="s">
         <v>716</v>
-      </c>
-      <c r="B80" s="14" t="s">
-        <v>717</v>
-      </c>
-      <c r="C80" s="9" t="s">
-        <v>718</v>
-      </c>
-      <c r="D80" s="9" t="s">
-        <v>719</v>
-      </c>
-      <c r="E80" s="9" t="s">
-        <v>720</v>
       </c>
       <c r="F80" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="G80" s="9" t="s">
+      <c r="G80" s="8" t="s">
         <v>89</v>
       </c>
       <c r="H80" s="9" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="81" spans="1:8" s="7" customFormat="1">
-      <c r="A81" s="12" t="s">
+    <row r="81" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="10" t="s">
+        <v>717</v>
+      </c>
+      <c r="B81" s="11" t="s">
+        <v>718</v>
+      </c>
+      <c r="C81" s="9" t="s">
+        <v>719</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>721</v>
-      </c>
-      <c r="B81" s="14" t="s">
-        <v>722</v>
-      </c>
-      <c r="C81" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="D81" s="9" t="s">
-        <v>724</v>
-      </c>
-      <c r="E81" s="9" t="s">
-        <v>725</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>355</v>
@@ -7331,662 +7630,662 @@
         <v>11</v>
       </c>
     </row>
-    <row r="82" spans="1:8" s="7" customFormat="1">
+    <row r="82" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A82" s="7" t="s">
+        <v>722</v>
+      </c>
+      <c r="B82" s="7" t="s">
+        <v>723</v>
+      </c>
+      <c r="C82" s="7" t="s">
+        <v>724</v>
+      </c>
+      <c r="D82" s="7" t="s">
+        <v>725</v>
+      </c>
+      <c r="E82" s="7" t="s">
         <v>726</v>
-      </c>
-      <c r="B82" s="7" t="s">
-        <v>727</v>
-      </c>
-      <c r="C82" s="7" t="s">
-        <v>728</v>
-      </c>
-      <c r="D82" s="7" t="s">
-        <v>729</v>
-      </c>
-      <c r="E82" s="7" t="s">
-        <v>730</v>
       </c>
       <c r="F82" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G82" s="7" t="s">
+      <c r="G82" s="8" t="s">
         <v>91</v>
       </c>
       <c r="H82" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="83" spans="1:8" s="7" customFormat="1">
+    <row r="83" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A83" s="7" t="s">
+        <v>727</v>
+      </c>
+      <c r="B83" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="C83" s="7" t="s">
+        <v>729</v>
+      </c>
+      <c r="D83" s="7" t="s">
+        <v>730</v>
+      </c>
+      <c r="E83" s="7" t="s">
         <v>731</v>
-      </c>
-      <c r="B83" s="7" t="s">
-        <v>732</v>
-      </c>
-      <c r="C83" s="7" t="s">
-        <v>733</v>
-      </c>
-      <c r="D83" s="7" t="s">
-        <v>734</v>
-      </c>
-      <c r="E83" s="7" t="s">
-        <v>735</v>
       </c>
       <c r="F83" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G83" s="7" t="s">
+      <c r="G83" s="9" t="s">
         <v>92</v>
       </c>
       <c r="H83" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="84" spans="1:8" s="7" customFormat="1">
+    <row r="84" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A84" s="7" t="s">
-        <v>736</v>
+        <v>732</v>
       </c>
       <c r="B84" s="7" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D84" s="7" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="E84" s="7" t="s">
-        <v>737</v>
+        <v>733</v>
       </c>
       <c r="F84" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G84" s="7" t="s">
+      <c r="G84" s="8" t="s">
         <v>93</v>
       </c>
       <c r="H84" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="85" spans="1:8" s="7" customFormat="1">
+    <row r="85" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A85" s="7" t="s">
+        <v>734</v>
+      </c>
+      <c r="B85" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="C85" s="7" t="s">
+        <v>736</v>
+      </c>
+      <c r="D85" s="7" t="s">
+        <v>737</v>
+      </c>
+      <c r="E85" s="7" t="s">
         <v>738</v>
-      </c>
-      <c r="B85" s="7" t="s">
-        <v>739</v>
-      </c>
-      <c r="C85" s="7" t="s">
-        <v>740</v>
-      </c>
-      <c r="D85" s="7" t="s">
-        <v>741</v>
-      </c>
-      <c r="E85" s="7" t="s">
-        <v>742</v>
       </c>
       <c r="F85" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G85" s="7" t="s">
+      <c r="G85" s="9" t="s">
         <v>94</v>
       </c>
       <c r="H85" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="86" spans="1:8" s="7" customFormat="1">
+    <row r="86" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A86" s="7" t="s">
+        <v>739</v>
+      </c>
+      <c r="B86" s="7" t="s">
+        <v>740</v>
+      </c>
+      <c r="C86" s="7" t="s">
+        <v>741</v>
+      </c>
+      <c r="D86" s="7" t="s">
+        <v>742</v>
+      </c>
+      <c r="E86" s="7" t="s">
         <v>743</v>
-      </c>
-      <c r="B86" s="7" t="s">
-        <v>744</v>
-      </c>
-      <c r="C86" s="7" t="s">
-        <v>745</v>
-      </c>
-      <c r="D86" s="7" t="s">
-        <v>746</v>
-      </c>
-      <c r="E86" s="7" t="s">
-        <v>747</v>
       </c>
       <c r="F86" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G86" s="7" t="s">
+      <c r="G86" s="8" t="s">
         <v>95</v>
       </c>
       <c r="H86" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="87" spans="1:8" s="7" customFormat="1">
+    <row r="87" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A87" s="7" t="s">
+        <v>744</v>
+      </c>
+      <c r="B87" s="7" t="s">
+        <v>745</v>
+      </c>
+      <c r="C87" s="7" t="s">
+        <v>746</v>
+      </c>
+      <c r="D87" s="7" t="s">
+        <v>747</v>
+      </c>
+      <c r="E87" s="7" t="s">
         <v>748</v>
-      </c>
-      <c r="B87" s="7" t="s">
-        <v>749</v>
-      </c>
-      <c r="C87" s="7" t="s">
-        <v>750</v>
-      </c>
-      <c r="D87" s="7" t="s">
-        <v>751</v>
-      </c>
-      <c r="E87" s="7" t="s">
-        <v>752</v>
       </c>
       <c r="F87" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G87" s="7" t="s">
+      <c r="G87" s="9" t="s">
         <v>96</v>
       </c>
       <c r="H87" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="88" spans="1:8" s="7" customFormat="1">
+    <row r="88" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A88" s="7" t="s">
+        <v>749</v>
+      </c>
+      <c r="B88" s="7" t="s">
+        <v>750</v>
+      </c>
+      <c r="C88" s="7" t="s">
+        <v>751</v>
+      </c>
+      <c r="D88" s="7" t="s">
+        <v>752</v>
+      </c>
+      <c r="E88" s="7" t="s">
         <v>753</v>
-      </c>
-      <c r="B88" s="7" t="s">
-        <v>754</v>
-      </c>
-      <c r="C88" s="7" t="s">
-        <v>755</v>
-      </c>
-      <c r="D88" s="7" t="s">
-        <v>756</v>
-      </c>
-      <c r="E88" s="7" t="s">
-        <v>757</v>
       </c>
       <c r="F88" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G88" s="7" t="s">
+      <c r="G88" s="8" t="s">
         <v>97</v>
       </c>
       <c r="H88" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="89" spans="1:8" s="7" customFormat="1">
+    <row r="89" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A89" s="7" t="s">
+        <v>754</v>
+      </c>
+      <c r="B89" s="7" t="s">
+        <v>755</v>
+      </c>
+      <c r="C89" s="7" t="s">
+        <v>756</v>
+      </c>
+      <c r="D89" s="7" t="s">
+        <v>757</v>
+      </c>
+      <c r="E89" s="7" t="s">
         <v>758</v>
-      </c>
-      <c r="B89" s="7" t="s">
-        <v>759</v>
-      </c>
-      <c r="C89" s="7" t="s">
-        <v>760</v>
-      </c>
-      <c r="D89" s="7" t="s">
-        <v>761</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>762</v>
       </c>
       <c r="F89" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G89" s="7" t="s">
+      <c r="G89" s="9" t="s">
         <v>98</v>
       </c>
       <c r="H89" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="90" spans="1:8" s="7" customFormat="1">
+    <row r="90" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A90" s="7" t="s">
+        <v>759</v>
+      </c>
+      <c r="B90" s="7" t="s">
+        <v>760</v>
+      </c>
+      <c r="C90" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="D90" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="E90" s="7" t="s">
         <v>763</v>
-      </c>
-      <c r="B90" s="7" t="s">
-        <v>764</v>
-      </c>
-      <c r="C90" s="7" t="s">
-        <v>765</v>
-      </c>
-      <c r="D90" s="7" t="s">
-        <v>766</v>
-      </c>
-      <c r="E90" s="7" t="s">
-        <v>767</v>
       </c>
       <c r="F90" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G90" s="7" t="s">
+      <c r="G90" s="8" t="s">
         <v>99</v>
       </c>
       <c r="H90" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="91" spans="1:8" s="7" customFormat="1">
+    <row r="91" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A91" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="B91" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="C91" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="D91" s="7" t="s">
+        <v>767</v>
+      </c>
+      <c r="E91" s="7" t="s">
         <v>768</v>
-      </c>
-      <c r="B91" s="7" t="s">
-        <v>769</v>
-      </c>
-      <c r="C91" s="7" t="s">
-        <v>770</v>
-      </c>
-      <c r="D91" s="7" t="s">
-        <v>771</v>
-      </c>
-      <c r="E91" s="7" t="s">
-        <v>772</v>
       </c>
       <c r="F91" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G91" s="7" t="s">
+      <c r="G91" s="9" t="s">
         <v>100</v>
       </c>
       <c r="H91" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="92" spans="1:8" s="7" customFormat="1">
+    <row r="92" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A92" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="B92" s="7" t="s">
+        <v>770</v>
+      </c>
+      <c r="C92" s="7" t="s">
+        <v>771</v>
+      </c>
+      <c r="D92" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="E92" s="7" t="s">
         <v>773</v>
-      </c>
-      <c r="B92" s="7" t="s">
-        <v>774</v>
-      </c>
-      <c r="C92" s="7" t="s">
-        <v>775</v>
-      </c>
-      <c r="D92" s="7" t="s">
-        <v>776</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>777</v>
       </c>
       <c r="F92" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G92" s="7" t="s">
+      <c r="G92" s="8" t="s">
         <v>101</v>
       </c>
       <c r="H92" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="93" spans="1:8" s="7" customFormat="1">
+    <row r="93" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A93" s="7" t="s">
+        <v>774</v>
+      </c>
+      <c r="B93" s="7" t="s">
+        <v>775</v>
+      </c>
+      <c r="C93" s="7" t="s">
+        <v>776</v>
+      </c>
+      <c r="D93" s="7" t="s">
+        <v>777</v>
+      </c>
+      <c r="E93" s="7" t="s">
         <v>778</v>
-      </c>
-      <c r="B93" s="7" t="s">
-        <v>779</v>
-      </c>
-      <c r="C93" s="7" t="s">
-        <v>780</v>
-      </c>
-      <c r="D93" s="7" t="s">
-        <v>781</v>
-      </c>
-      <c r="E93" s="7" t="s">
-        <v>782</v>
       </c>
       <c r="F93" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G93" s="7" t="s">
+      <c r="G93" s="9" t="s">
         <v>102</v>
       </c>
       <c r="H93" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="94" spans="1:8" s="7" customFormat="1">
+    <row r="94" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A94" s="7" t="s">
+        <v>779</v>
+      </c>
+      <c r="B94" s="7" t="s">
+        <v>780</v>
+      </c>
+      <c r="C94" s="7" t="s">
+        <v>781</v>
+      </c>
+      <c r="D94" s="7" t="s">
+        <v>782</v>
+      </c>
+      <c r="E94" s="7" t="s">
         <v>783</v>
-      </c>
-      <c r="B94" s="7" t="s">
-        <v>784</v>
-      </c>
-      <c r="C94" s="7" t="s">
-        <v>785</v>
-      </c>
-      <c r="D94" s="7" t="s">
-        <v>786</v>
-      </c>
-      <c r="E94" s="7" t="s">
-        <v>787</v>
       </c>
       <c r="F94" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G94" s="7" t="s">
+      <c r="G94" s="8" t="s">
         <v>103</v>
       </c>
       <c r="H94" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="95" spans="1:8" s="7" customFormat="1">
+    <row r="95" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A95" s="7" t="s">
+        <v>784</v>
+      </c>
+      <c r="B95" s="7" t="s">
+        <v>785</v>
+      </c>
+      <c r="C95" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="D95" s="7" t="s">
+        <v>787</v>
+      </c>
+      <c r="E95" s="7" t="s">
         <v>788</v>
-      </c>
-      <c r="B95" s="7" t="s">
-        <v>789</v>
-      </c>
-      <c r="C95" s="7" t="s">
-        <v>790</v>
-      </c>
-      <c r="D95" s="7" t="s">
-        <v>791</v>
-      </c>
-      <c r="E95" s="7" t="s">
-        <v>792</v>
       </c>
       <c r="F95" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G95" s="7" t="s">
+      <c r="G95" s="9" t="s">
         <v>104</v>
       </c>
       <c r="H95" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="96" spans="1:8" s="7" customFormat="1">
+    <row r="96" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A96" s="7" t="s">
-        <v>793</v>
+        <v>789</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="D96" s="7" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="E96" s="7" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="F96" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G96" s="7" t="s">
+      <c r="G96" s="8" t="s">
         <v>105</v>
       </c>
       <c r="H96" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="97" spans="1:8" s="7" customFormat="1">
+    <row r="97" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A97" s="7" t="s">
+        <v>792</v>
+      </c>
+      <c r="B97" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="C97" s="7" t="s">
+        <v>794</v>
+      </c>
+      <c r="D97" s="7" t="s">
+        <v>795</v>
+      </c>
+      <c r="E97" s="7" t="s">
         <v>796</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>797</v>
-      </c>
-      <c r="C97" s="7" t="s">
-        <v>798</v>
-      </c>
-      <c r="D97" s="7" t="s">
-        <v>799</v>
-      </c>
-      <c r="E97" s="7" t="s">
-        <v>800</v>
       </c>
       <c r="F97" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G97" s="7" t="s">
+      <c r="G97" s="9" t="s">
         <v>106</v>
       </c>
       <c r="H97" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="98" spans="1:8" s="7" customFormat="1">
+    <row r="98" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A98" s="7" t="s">
+        <v>797</v>
+      </c>
+      <c r="B98" s="7" t="s">
+        <v>798</v>
+      </c>
+      <c r="C98" s="7" t="s">
+        <v>799</v>
+      </c>
+      <c r="D98" s="7" t="s">
+        <v>800</v>
+      </c>
+      <c r="E98" s="7" t="s">
         <v>801</v>
-      </c>
-      <c r="B98" s="7" t="s">
-        <v>802</v>
-      </c>
-      <c r="C98" s="7" t="s">
-        <v>803</v>
-      </c>
-      <c r="D98" s="7" t="s">
-        <v>804</v>
-      </c>
-      <c r="E98" s="7" t="s">
-        <v>805</v>
       </c>
       <c r="F98" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G98" s="7" t="s">
+      <c r="G98" s="8" t="s">
         <v>107</v>
       </c>
       <c r="H98" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="99" spans="1:8" s="7" customFormat="1">
+    <row r="99" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A99" s="7" t="s">
-        <v>806</v>
+        <v>802</v>
       </c>
       <c r="B99" s="7" t="s">
+        <v>786</v>
+      </c>
+      <c r="C99" s="7" t="s">
+        <v>633</v>
+      </c>
+      <c r="D99" s="7" t="s">
+        <v>634</v>
+      </c>
+      <c r="E99" s="7" t="s">
         <v>790</v>
-      </c>
-      <c r="C99" s="7" t="s">
-        <v>637</v>
-      </c>
-      <c r="D99" s="7" t="s">
-        <v>638</v>
-      </c>
-      <c r="E99" s="7" t="s">
-        <v>794</v>
       </c>
       <c r="F99" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G99" s="7" t="s">
+      <c r="G99" s="9" t="s">
         <v>108</v>
       </c>
       <c r="H99" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="100" spans="1:8" s="7" customFormat="1">
+    <row r="100" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A100" s="7" t="s">
-        <v>807</v>
+        <v>803</v>
       </c>
       <c r="B100" s="7" t="s">
-        <v>794</v>
+        <v>790</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="D100" s="7" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="E100" s="7" t="s">
-        <v>795</v>
+        <v>791</v>
       </c>
       <c r="F100" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G100" s="7" t="s">
+      <c r="G100" s="8" t="s">
         <v>109</v>
       </c>
       <c r="H100" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="101" spans="1:8" s="7" customFormat="1">
+    <row r="101" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A101" s="7" t="s">
+        <v>804</v>
+      </c>
+      <c r="B101" s="7" t="s">
+        <v>805</v>
+      </c>
+      <c r="C101" s="7" t="s">
+        <v>806</v>
+      </c>
+      <c r="D101" s="7" t="s">
+        <v>807</v>
+      </c>
+      <c r="E101" s="7" t="s">
         <v>808</v>
-      </c>
-      <c r="B101" s="7" t="s">
-        <v>809</v>
-      </c>
-      <c r="C101" s="7" t="s">
-        <v>810</v>
-      </c>
-      <c r="D101" s="7" t="s">
-        <v>811</v>
-      </c>
-      <c r="E101" s="7" t="s">
-        <v>812</v>
       </c>
       <c r="F101" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G101" s="7" t="s">
+      <c r="G101" s="9" t="s">
         <v>110</v>
       </c>
       <c r="H101" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="102" spans="1:8" s="7" customFormat="1">
+    <row r="102" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A102" s="7" t="s">
+        <v>809</v>
+      </c>
+      <c r="B102" s="7" t="s">
+        <v>810</v>
+      </c>
+      <c r="C102" s="7" t="s">
+        <v>811</v>
+      </c>
+      <c r="D102" s="7" t="s">
+        <v>812</v>
+      </c>
+      <c r="E102" s="7" t="s">
         <v>813</v>
-      </c>
-      <c r="B102" s="7" t="s">
-        <v>814</v>
-      </c>
-      <c r="C102" s="7" t="s">
-        <v>815</v>
-      </c>
-      <c r="D102" s="7" t="s">
-        <v>816</v>
-      </c>
-      <c r="E102" s="7" t="s">
-        <v>817</v>
       </c>
       <c r="F102" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G102" s="7" t="s">
+      <c r="G102" s="8" t="s">
         <v>111</v>
       </c>
       <c r="H102" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="103" spans="1:8" s="7" customFormat="1">
+    <row r="103" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A103" s="7" t="s">
+        <v>814</v>
+      </c>
+      <c r="B103" s="7" t="s">
+        <v>815</v>
+      </c>
+      <c r="C103" s="7" t="s">
+        <v>816</v>
+      </c>
+      <c r="D103" s="7" t="s">
+        <v>817</v>
+      </c>
+      <c r="E103" s="7" t="s">
         <v>818</v>
-      </c>
-      <c r="B103" s="7" t="s">
-        <v>819</v>
-      </c>
-      <c r="C103" s="7" t="s">
-        <v>820</v>
-      </c>
-      <c r="D103" s="7" t="s">
-        <v>821</v>
-      </c>
-      <c r="E103" s="7" t="s">
-        <v>822</v>
       </c>
       <c r="F103" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G103" s="7" t="s">
+      <c r="G103" s="9" t="s">
         <v>112</v>
       </c>
       <c r="H103" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="104" spans="1:8" s="7" customFormat="1">
+    <row r="104" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A104" s="7" t="s">
+        <v>819</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>820</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>821</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>822</v>
+      </c>
+      <c r="E104" s="7" t="s">
         <v>823</v>
-      </c>
-      <c r="B104" s="7" t="s">
-        <v>824</v>
-      </c>
-      <c r="C104" s="7" t="s">
-        <v>825</v>
-      </c>
-      <c r="D104" s="7" t="s">
-        <v>826</v>
-      </c>
-      <c r="E104" s="7" t="s">
-        <v>827</v>
       </c>
       <c r="F104" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G104" s="7" t="s">
+      <c r="G104" s="8" t="s">
         <v>113</v>
       </c>
       <c r="H104" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="105" spans="1:8" s="7" customFormat="1">
+    <row r="105" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A105" s="7" t="s">
+        <v>824</v>
+      </c>
+      <c r="B105" s="7" t="s">
+        <v>825</v>
+      </c>
+      <c r="C105" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="D105" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="E105" s="7" t="s">
         <v>828</v>
-      </c>
-      <c r="B105" s="7" t="s">
-        <v>829</v>
-      </c>
-      <c r="C105" s="7" t="s">
-        <v>830</v>
-      </c>
-      <c r="D105" s="7" t="s">
-        <v>831</v>
-      </c>
-      <c r="E105" s="7" t="s">
-        <v>832</v>
       </c>
       <c r="F105" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G105" s="7" t="s">
+      <c r="G105" s="9" t="s">
         <v>114</v>
       </c>
       <c r="H105" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="106" spans="1:8" s="7" customFormat="1">
+    <row r="106" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A106" s="7" t="s">
+        <v>829</v>
+      </c>
+      <c r="B106" s="7" t="s">
+        <v>830</v>
+      </c>
+      <c r="C106" s="7" t="s">
+        <v>831</v>
+      </c>
+      <c r="D106" s="7" t="s">
+        <v>832</v>
+      </c>
+      <c r="E106" s="7" t="s">
         <v>833</v>
-      </c>
-      <c r="B106" s="7" t="s">
-        <v>834</v>
-      </c>
-      <c r="C106" s="7" t="s">
-        <v>835</v>
-      </c>
-      <c r="D106" s="7" t="s">
-        <v>836</v>
-      </c>
-      <c r="E106" s="7" t="s">
-        <v>837</v>
       </c>
       <c r="F106" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G106" s="7" t="s">
+      <c r="G106" s="8" t="s">
         <v>115</v>
       </c>
       <c r="H106" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="107" spans="1:8" s="7" customFormat="1">
+    <row r="107" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A107" s="7" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="B107" s="7" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C107" s="7" t="s">
         <v>350</v>
@@ -7998,24 +8297,24 @@
         <v>351</v>
       </c>
       <c r="F107" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G107" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="G107" s="9" t="s">
         <v>116</v>
       </c>
       <c r="H107" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="108" spans="1:8" s="7" customFormat="1">
+    <row r="108" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A108" s="7" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="B108" s="7" t="s">
         <v>350</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="D108" s="7" t="s">
         <v>351</v>
@@ -8026,97 +8325,97 @@
       <c r="F108" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G108" s="7" t="s">
+      <c r="G108" s="8" t="s">
         <v>117</v>
       </c>
       <c r="H108" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="109" spans="1:8" s="7" customFormat="1">
+    <row r="109" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A109" s="7" t="s">
+        <v>837</v>
+      </c>
+      <c r="B109" s="7" t="s">
+        <v>838</v>
+      </c>
+      <c r="C109" s="7" t="s">
+        <v>839</v>
+      </c>
+      <c r="D109" s="7" t="s">
+        <v>840</v>
+      </c>
+      <c r="E109" s="7" t="s">
         <v>841</v>
-      </c>
-      <c r="B109" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="C109" s="7" t="s">
-        <v>843</v>
-      </c>
-      <c r="D109" s="7" t="s">
-        <v>844</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>845</v>
       </c>
       <c r="F109" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G109" s="7" t="s">
+      <c r="G109" s="9" t="s">
         <v>118</v>
       </c>
       <c r="H109" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="110" spans="1:8" s="7" customFormat="1">
+    <row r="110" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A110" s="7" t="s">
         <v>360</v>
       </c>
       <c r="B110" s="7" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="D110" s="7" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="E110" s="7" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F110" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G110" s="7" t="s">
+      <c r="G110" s="8" t="s">
         <v>119</v>
       </c>
       <c r="H110" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="111" spans="1:8" s="7" customFormat="1">
+    <row r="111" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A111" s="7" t="s">
+        <v>846</v>
+      </c>
+      <c r="B111" s="7" t="s">
+        <v>847</v>
+      </c>
+      <c r="C111" s="7" t="s">
+        <v>848</v>
+      </c>
+      <c r="D111" s="7" t="s">
+        <v>849</v>
+      </c>
+      <c r="E111" s="7" t="s">
         <v>850</v>
-      </c>
-      <c r="B111" s="7" t="s">
-        <v>851</v>
-      </c>
-      <c r="C111" s="7" t="s">
-        <v>852</v>
-      </c>
-      <c r="D111" s="7" t="s">
-        <v>853</v>
-      </c>
-      <c r="E111" s="7" t="s">
-        <v>854</v>
       </c>
       <c r="F111" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G111" s="7" t="s">
+      <c r="G111" s="9" t="s">
         <v>120</v>
       </c>
       <c r="H111" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="112" spans="1:8" s="7" customFormat="1">
+    <row r="112" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A112" s="7" t="s">
-        <v>855</v>
+        <v>851</v>
       </c>
       <c r="B112" s="7" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="C112" s="7" t="s">
         <v>350</v>
@@ -8130,51 +8429,51 @@
       <c r="F112" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G112" s="7" t="s">
+      <c r="G112" s="8" t="s">
         <v>121</v>
       </c>
       <c r="H112" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="113" spans="1:8" s="7" customFormat="1">
+    <row r="113" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A113" s="7" t="s">
+        <v>852</v>
+      </c>
+      <c r="B113" s="7" t="s">
+        <v>853</v>
+      </c>
+      <c r="C113" s="7" t="s">
+        <v>854</v>
+      </c>
+      <c r="D113" s="7" t="s">
+        <v>855</v>
+      </c>
+      <c r="E113" s="7" t="s">
         <v>856</v>
-      </c>
-      <c r="B113" s="7" t="s">
-        <v>857</v>
-      </c>
-      <c r="C113" s="7" t="s">
-        <v>858</v>
-      </c>
-      <c r="D113" s="7" t="s">
-        <v>859</v>
-      </c>
-      <c r="E113" s="7" t="s">
-        <v>860</v>
       </c>
       <c r="F113" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G113" s="7" t="s">
+      <c r="G113" s="9" t="s">
         <v>122</v>
       </c>
       <c r="H113" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="114" spans="1:8" s="7" customFormat="1">
+    <row r="114" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A114" s="7" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B114" s="7" t="s">
         <v>350</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D114" s="7" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="E114" s="7" t="s">
         <v>357</v>
@@ -8182,395 +8481,395 @@
       <c r="F114" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G114" s="7" t="s">
+      <c r="G114" s="8" t="s">
         <v>123</v>
       </c>
       <c r="H114" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="115" spans="1:8" s="7" customFormat="1">
+    <row r="115" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A115" s="7" t="s">
+        <v>859</v>
+      </c>
+      <c r="B115" s="7" t="s">
+        <v>860</v>
+      </c>
+      <c r="C115" s="7" t="s">
+        <v>861</v>
+      </c>
+      <c r="D115" s="7" t="s">
+        <v>862</v>
+      </c>
+      <c r="E115" s="7" t="s">
         <v>863</v>
-      </c>
-      <c r="B115" s="7" t="s">
-        <v>864</v>
-      </c>
-      <c r="C115" s="7" t="s">
-        <v>865</v>
-      </c>
-      <c r="D115" s="7" t="s">
-        <v>866</v>
-      </c>
-      <c r="E115" s="7" t="s">
-        <v>867</v>
       </c>
       <c r="F115" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G115" s="7" t="s">
+      <c r="G115" s="9" t="s">
         <v>124</v>
       </c>
       <c r="H115" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="116" spans="1:8" s="7" customFormat="1">
+    <row r="116" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A116" s="7" t="s">
+        <v>864</v>
+      </c>
+      <c r="B116" s="7" t="s">
+        <v>865</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>866</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>867</v>
+      </c>
+      <c r="E116" s="7" t="s">
         <v>868</v>
-      </c>
-      <c r="B116" s="7" t="s">
-        <v>869</v>
-      </c>
-      <c r="C116" s="7" t="s">
-        <v>870</v>
-      </c>
-      <c r="D116" s="7" t="s">
-        <v>871</v>
-      </c>
-      <c r="E116" s="7" t="s">
-        <v>872</v>
       </c>
       <c r="F116" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G116" s="7" t="s">
+      <c r="G116" s="8" t="s">
         <v>125</v>
       </c>
       <c r="H116" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="117" spans="1:8" s="7" customFormat="1">
+    <row r="117" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A117" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="B117" s="7" t="s">
+        <v>870</v>
+      </c>
+      <c r="C117" s="7" t="s">
+        <v>871</v>
+      </c>
+      <c r="D117" s="7" t="s">
+        <v>872</v>
+      </c>
+      <c r="E117" s="7" t="s">
         <v>873</v>
-      </c>
-      <c r="B117" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="C117" s="7" t="s">
-        <v>875</v>
-      </c>
-      <c r="D117" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="E117" s="7" t="s">
-        <v>877</v>
       </c>
       <c r="F117" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G117" s="7" t="s">
+      <c r="G117" s="9" t="s">
         <v>126</v>
       </c>
       <c r="H117" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="118" spans="1:8" s="7" customFormat="1">
+    <row r="118" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A118" s="7" t="s">
+        <v>874</v>
+      </c>
+      <c r="B118" s="7" t="s">
+        <v>875</v>
+      </c>
+      <c r="C118" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="D118" s="7" t="s">
+        <v>877</v>
+      </c>
+      <c r="E118" s="7" t="s">
         <v>878</v>
-      </c>
-      <c r="B118" s="7" t="s">
-        <v>879</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>880</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>881</v>
-      </c>
-      <c r="E118" s="7" t="s">
-        <v>882</v>
       </c>
       <c r="F118" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G118" s="7" t="s">
+      <c r="G118" s="8" t="s">
         <v>127</v>
       </c>
       <c r="H118" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="119" spans="1:8" s="7" customFormat="1">
+    <row r="119" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A119" s="7" t="s">
+        <v>879</v>
+      </c>
+      <c r="B119" s="7" t="s">
+        <v>880</v>
+      </c>
+      <c r="C119" s="7" t="s">
+        <v>881</v>
+      </c>
+      <c r="D119" s="7" t="s">
+        <v>882</v>
+      </c>
+      <c r="E119" s="7" t="s">
         <v>883</v>
-      </c>
-      <c r="B119" s="7" t="s">
-        <v>884</v>
-      </c>
-      <c r="C119" s="7" t="s">
-        <v>885</v>
-      </c>
-      <c r="D119" s="7" t="s">
-        <v>886</v>
-      </c>
-      <c r="E119" s="7" t="s">
-        <v>887</v>
       </c>
       <c r="F119" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G119" s="7" t="s">
+      <c r="G119" s="9" t="s">
         <v>128</v>
       </c>
       <c r="H119" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="120" spans="1:8" s="7" customFormat="1">
+    <row r="120" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A120" s="7" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="B120" s="7" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="D120" s="7" t="s">
-        <v>886</v>
+        <v>882</v>
       </c>
       <c r="E120" s="7" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="F120" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G120" s="7" t="s">
+      <c r="G120" s="8" t="s">
         <v>129</v>
       </c>
       <c r="H120" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="121" spans="1:8" s="7" customFormat="1">
+    <row r="121" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A121" s="7" t="s">
+        <v>886</v>
+      </c>
+      <c r="B121" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="C121" s="7" t="s">
+        <v>888</v>
+      </c>
+      <c r="D121" s="7" t="s">
+        <v>889</v>
+      </c>
+      <c r="E121" s="7" t="s">
         <v>890</v>
-      </c>
-      <c r="B121" s="7" t="s">
-        <v>891</v>
-      </c>
-      <c r="C121" s="7" t="s">
-        <v>892</v>
-      </c>
-      <c r="D121" s="7" t="s">
-        <v>893</v>
-      </c>
-      <c r="E121" s="7" t="s">
-        <v>894</v>
       </c>
       <c r="F121" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G121" s="7" t="s">
+      <c r="G121" s="9" t="s">
         <v>130</v>
       </c>
       <c r="H121" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="122" spans="1:8" s="7" customFormat="1">
+    <row r="122" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A122" s="7" t="s">
+        <v>891</v>
+      </c>
+      <c r="B122" s="7" t="s">
+        <v>892</v>
+      </c>
+      <c r="C122" s="7" t="s">
+        <v>893</v>
+      </c>
+      <c r="D122" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="E122" s="7" t="s">
         <v>895</v>
-      </c>
-      <c r="B122" s="7" t="s">
-        <v>896</v>
-      </c>
-      <c r="C122" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="D122" s="7" t="s">
-        <v>898</v>
-      </c>
-      <c r="E122" s="7" t="s">
-        <v>899</v>
       </c>
       <c r="F122" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G122" s="7" t="s">
+      <c r="G122" s="8" t="s">
         <v>131</v>
       </c>
       <c r="H122" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="123" spans="1:8" s="7" customFormat="1">
+    <row r="123" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A123" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="C123" s="7" t="s">
+        <v>898</v>
+      </c>
+      <c r="D123" s="7" t="s">
+        <v>899</v>
+      </c>
+      <c r="E123" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="F123" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="G123" s="9" t="s">
+        <v>132</v>
+      </c>
+      <c r="H123" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="124" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A124" s="7" t="s">
         <v>901</v>
       </c>
-      <c r="C123" s="7" t="s">
+      <c r="B124" s="7" t="s">
         <v>902</v>
       </c>
-      <c r="D123" s="7" t="s">
+      <c r="C124" s="7" t="s">
         <v>903</v>
       </c>
-      <c r="E123" s="7" t="s">
+      <c r="D124" s="7" t="s">
         <v>904</v>
       </c>
-      <c r="F123" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G123" s="7" t="s">
-        <v>132</v>
-      </c>
-      <c r="H123" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="124" spans="1:8" s="7" customFormat="1">
-      <c r="A124" s="7" t="s">
+      <c r="E124" s="7" t="s">
         <v>905</v>
-      </c>
-      <c r="B124" s="7" t="s">
-        <v>906</v>
-      </c>
-      <c r="C124" s="7" t="s">
-        <v>907</v>
-      </c>
-      <c r="D124" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="E124" s="7" t="s">
-        <v>909</v>
       </c>
       <c r="F124" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="G124" s="7" t="s">
+      <c r="G124" s="8" t="s">
         <v>133</v>
       </c>
       <c r="H124" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="125" spans="1:8" s="7" customFormat="1">
+    <row r="125" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A125" s="7" t="s">
+        <v>906</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="C125" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="D125" s="7" t="s">
+        <v>909</v>
+      </c>
+      <c r="E125" s="7" t="s">
         <v>910</v>
       </c>
-      <c r="B125" s="7" t="s">
+      <c r="F125" s="7" t="s">
+        <v>447</v>
+      </c>
+      <c r="G125" s="9" t="s">
+        <v>134</v>
+      </c>
+      <c r="H125" s="7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="126" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A126" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="C125" s="7" t="s">
+      <c r="B126" s="7" t="s">
         <v>912</v>
       </c>
-      <c r="D125" s="7" t="s">
+      <c r="C126" s="7" t="s">
         <v>913</v>
       </c>
-      <c r="E125" s="7" t="s">
+      <c r="D126" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="F125" s="7" t="s">
-        <v>451</v>
-      </c>
-      <c r="G125" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="H125" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8" s="7" customFormat="1">
-      <c r="A126" s="7" t="s">
+      <c r="E126" s="7" t="s">
         <v>915</v>
-      </c>
-      <c r="B126" s="7" t="s">
-        <v>916</v>
-      </c>
-      <c r="C126" s="7" t="s">
-        <v>917</v>
-      </c>
-      <c r="D126" s="7" t="s">
-        <v>918</v>
-      </c>
-      <c r="E126" s="7" t="s">
-        <v>919</v>
       </c>
       <c r="F126" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="G126" s="7" t="s">
+      <c r="G126" s="8" t="s">
         <v>135</v>
       </c>
       <c r="H126" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="127" spans="1:8" s="7" customFormat="1">
+    <row r="127" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A127" s="7" t="s">
+        <v>916</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>917</v>
+      </c>
+      <c r="C127" s="7" t="s">
+        <v>918</v>
+      </c>
+      <c r="D127" s="7" t="s">
+        <v>919</v>
+      </c>
+      <c r="E127" s="7" t="s">
         <v>920</v>
-      </c>
-      <c r="B127" s="7" t="s">
-        <v>921</v>
-      </c>
-      <c r="C127" s="7" t="s">
-        <v>922</v>
-      </c>
-      <c r="D127" s="7" t="s">
-        <v>923</v>
-      </c>
-      <c r="E127" s="7" t="s">
-        <v>924</v>
       </c>
       <c r="F127" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="G127" s="7" t="s">
+      <c r="G127" s="9" t="s">
         <v>136</v>
       </c>
       <c r="H127" s="7" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="128" spans="1:8" s="7" customFormat="1" ht="26">
-      <c r="A128" s="15" t="s">
+    <row r="128" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A128" s="8" t="s">
+        <v>921</v>
+      </c>
+      <c r="B128" s="8" t="s">
+        <v>922</v>
+      </c>
+      <c r="C128" s="8" t="s">
+        <v>923</v>
+      </c>
+      <c r="D128" s="8" t="s">
+        <v>924</v>
+      </c>
+      <c r="E128" s="8" t="s">
         <v>925</v>
-      </c>
-      <c r="B128" s="8" t="s">
-        <v>926</v>
-      </c>
-      <c r="C128" s="8" t="s">
-        <v>927</v>
-      </c>
-      <c r="D128" s="8" t="s">
-        <v>928</v>
-      </c>
-      <c r="E128" s="8" t="s">
-        <v>929</v>
       </c>
       <c r="F128" s="8" t="s">
         <v>353</v>
       </c>
-      <c r="G128" s="9" t="s">
+      <c r="G128" s="8" t="s">
         <v>138</v>
       </c>
       <c r="H128" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="129" spans="1:8" s="7" customFormat="1" ht="26">
-      <c r="A129" s="15" t="s">
+    <row r="129" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A129" s="8" t="s">
+        <v>926</v>
+      </c>
+      <c r="B129" s="8" t="s">
+        <v>927</v>
+      </c>
+      <c r="C129" s="8" t="s">
+        <v>928</v>
+      </c>
+      <c r="D129" s="8" t="s">
+        <v>929</v>
+      </c>
+      <c r="E129" s="8" t="s">
         <v>930</v>
       </c>
-      <c r="B129" s="8" t="s">
-        <v>931</v>
-      </c>
-      <c r="C129" s="8" t="s">
-        <v>932</v>
-      </c>
-      <c r="D129" s="8" t="s">
-        <v>933</v>
-      </c>
-      <c r="E129" s="8" t="s">
-        <v>934</v>
-      </c>
       <c r="F129" s="8" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="G129" s="9" t="s">
         <v>139</v>
@@ -8579,47 +8878,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:8" s="7" customFormat="1" ht="52">
-      <c r="A130" s="16" t="s">
+    <row r="130" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A130" s="9" t="s">
+        <v>931</v>
+      </c>
+      <c r="B130" s="9" t="s">
+        <v>932</v>
+      </c>
+      <c r="C130" s="9" t="s">
+        <v>933</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>934</v>
+      </c>
+      <c r="E130" s="9" t="s">
         <v>935</v>
-      </c>
-      <c r="B130" s="9" t="s">
-        <v>936</v>
-      </c>
-      <c r="C130" s="9" t="s">
-        <v>937</v>
-      </c>
-      <c r="D130" s="9" t="s">
-        <v>938</v>
-      </c>
-      <c r="E130" s="9" t="s">
-        <v>939</v>
       </c>
       <c r="F130" s="9" t="s">
         <v>353</v>
       </c>
-      <c r="G130" s="9" t="s">
+      <c r="G130" s="8" t="s">
         <v>140</v>
       </c>
       <c r="H130" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:8" s="7" customFormat="1" ht="52">
-      <c r="A131" s="15" t="s">
+    <row r="131" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A131" s="8" t="s">
+        <v>936</v>
+      </c>
+      <c r="B131" s="8" t="s">
+        <v>937</v>
+      </c>
+      <c r="C131" s="8" t="s">
+        <v>938</v>
+      </c>
+      <c r="D131" s="8" t="s">
+        <v>939</v>
+      </c>
+      <c r="E131" s="8" t="s">
         <v>940</v>
-      </c>
-      <c r="B131" s="8" t="s">
-        <v>941</v>
-      </c>
-      <c r="C131" s="8" t="s">
-        <v>942</v>
-      </c>
-      <c r="D131" s="8" t="s">
-        <v>943</v>
-      </c>
-      <c r="E131" s="8" t="s">
-        <v>944</v>
       </c>
       <c r="F131" s="8" t="s">
         <v>355</v>
@@ -8631,47 +8930,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:8" s="7" customFormat="1" ht="52">
-      <c r="A132" s="15" t="s">
+    <row r="132" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A132" s="8" t="s">
+        <v>941</v>
+      </c>
+      <c r="B132" s="8" t="s">
+        <v>942</v>
+      </c>
+      <c r="C132" s="8" t="s">
+        <v>943</v>
+      </c>
+      <c r="D132" s="8" t="s">
+        <v>944</v>
+      </c>
+      <c r="E132" s="8" t="s">
         <v>945</v>
-      </c>
-      <c r="B132" s="8" t="s">
-        <v>946</v>
-      </c>
-      <c r="C132" s="8" t="s">
-        <v>947</v>
-      </c>
-      <c r="D132" s="8" t="s">
-        <v>948</v>
-      </c>
-      <c r="E132" s="8" t="s">
-        <v>949</v>
       </c>
       <c r="F132" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="G132" s="9" t="s">
+      <c r="G132" s="8" t="s">
         <v>142</v>
       </c>
       <c r="H132" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:8" s="7" customFormat="1" ht="39">
-      <c r="A133" s="16" t="s">
+    <row r="133" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A133" s="9" t="s">
+        <v>946</v>
+      </c>
+      <c r="B133" s="9" t="s">
+        <v>947</v>
+      </c>
+      <c r="C133" s="9" t="s">
+        <v>948</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>949</v>
+      </c>
+      <c r="E133" s="9" t="s">
         <v>950</v>
-      </c>
-      <c r="B133" s="9" t="s">
-        <v>951</v>
-      </c>
-      <c r="C133" s="9" t="s">
-        <v>952</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>953</v>
-      </c>
-      <c r="E133" s="9" t="s">
-        <v>954</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>355</v>
@@ -8683,50 +8982,50 @@
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:8" s="7" customFormat="1" ht="52">
-      <c r="A134" s="15" t="s">
+    <row r="134" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A134" s="8" t="s">
+        <v>951</v>
+      </c>
+      <c r="B134" s="8" t="s">
+        <v>952</v>
+      </c>
+      <c r="C134" s="8" t="s">
+        <v>953</v>
+      </c>
+      <c r="D134" s="8" t="s">
+        <v>954</v>
+      </c>
+      <c r="E134" s="8" t="s">
         <v>955</v>
-      </c>
-      <c r="B134" s="8" t="s">
-        <v>956</v>
-      </c>
-      <c r="C134" s="8" t="s">
-        <v>957</v>
-      </c>
-      <c r="D134" s="8" t="s">
-        <v>958</v>
-      </c>
-      <c r="E134" s="8" t="s">
-        <v>959</v>
       </c>
       <c r="F134" s="8" t="s">
         <v>355</v>
       </c>
-      <c r="G134" s="9" t="s">
+      <c r="G134" s="8" t="s">
         <v>159</v>
       </c>
       <c r="H134" s="8" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:8" s="7" customFormat="1">
-      <c r="A135" s="17" t="s">
-        <v>960</v>
-      </c>
-      <c r="B135" s="17" t="s">
-        <v>970</v>
-      </c>
-      <c r="C135" s="17" t="s">
-        <v>971</v>
-      </c>
-      <c r="D135" s="17" t="s">
-        <v>972</v>
-      </c>
-      <c r="E135" s="17" t="s">
-        <v>973</v>
-      </c>
-      <c r="F135" s="17" t="s">
+    <row r="135" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="12" t="s">
+        <v>956</v>
+      </c>
+      <c r="B135" s="12" t="s">
+        <v>966</v>
+      </c>
+      <c r="C135" s="12" t="s">
         <v>967</v>
+      </c>
+      <c r="D135" s="12" t="s">
+        <v>968</v>
+      </c>
+      <c r="E135" s="12" t="s">
+        <v>969</v>
+      </c>
+      <c r="F135" s="12" t="s">
+        <v>963</v>
       </c>
       <c r="G135" s="9" t="s">
         <v>160</v>
@@ -8735,50 +9034,50 @@
         <v>137</v>
       </c>
     </row>
-    <row r="136" spans="1:8" s="7" customFormat="1">
-      <c r="A136" s="17" t="s">
+    <row r="136" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="12" t="s">
+        <v>971</v>
+      </c>
+      <c r="B136" s="12" t="s">
+        <v>972</v>
+      </c>
+      <c r="C136" s="12" t="s">
+        <v>973</v>
+      </c>
+      <c r="D136" s="12" t="s">
+        <v>974</v>
+      </c>
+      <c r="E136" s="12" t="s">
         <v>975</v>
       </c>
-      <c r="B136" s="17" t="s">
-        <v>976</v>
-      </c>
-      <c r="C136" s="17" t="s">
-        <v>977</v>
-      </c>
-      <c r="D136" s="17" t="s">
-        <v>978</v>
-      </c>
-      <c r="E136" s="17" t="s">
-        <v>979</v>
-      </c>
-      <c r="F136" s="17" t="s">
-        <v>961</v>
-      </c>
-      <c r="G136" s="9" t="s">
+      <c r="F136" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="G136" s="8" t="s">
         <v>161</v>
       </c>
       <c r="H136" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="137" spans="1:8" s="7" customFormat="1">
-      <c r="A137" s="17" t="s">
+    <row r="137" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A137" s="12" t="s">
+        <v>977</v>
+      </c>
+      <c r="B137" s="12" t="s">
+        <v>978</v>
+      </c>
+      <c r="C137" s="12" t="s">
+        <v>979</v>
+      </c>
+      <c r="D137" s="12" t="s">
+        <v>980</v>
+      </c>
+      <c r="E137" s="12" t="s">
         <v>981</v>
       </c>
-      <c r="B137" s="17" t="s">
-        <v>982</v>
-      </c>
-      <c r="C137" s="17" t="s">
-        <v>983</v>
-      </c>
-      <c r="D137" s="17" t="s">
-        <v>984</v>
-      </c>
-      <c r="E137" s="17" t="s">
-        <v>985</v>
-      </c>
-      <c r="F137" s="17" t="s">
-        <v>962</v>
+      <c r="F137" s="12" t="s">
+        <v>958</v>
       </c>
       <c r="G137" s="9" t="s">
         <v>162</v>
@@ -8787,50 +9086,50 @@
         <v>137</v>
       </c>
     </row>
-    <row r="138" spans="1:8" s="7" customFormat="1">
-      <c r="A138" s="17" t="s">
+    <row r="138" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="12" t="s">
+        <v>983</v>
+      </c>
+      <c r="B138" s="12" t="s">
+        <v>984</v>
+      </c>
+      <c r="C138" s="12" t="s">
+        <v>985</v>
+      </c>
+      <c r="D138" s="12" t="s">
+        <v>986</v>
+      </c>
+      <c r="E138" s="12" t="s">
         <v>987</v>
       </c>
-      <c r="B138" s="17" t="s">
-        <v>988</v>
-      </c>
-      <c r="C138" s="17" t="s">
-        <v>989</v>
-      </c>
-      <c r="D138" s="17" t="s">
-        <v>990</v>
-      </c>
-      <c r="E138" s="17" t="s">
-        <v>991</v>
-      </c>
-      <c r="F138" s="17" t="s">
-        <v>961</v>
-      </c>
-      <c r="G138" s="9" t="s">
+      <c r="F138" s="12" t="s">
+        <v>957</v>
+      </c>
+      <c r="G138" s="8" t="s">
         <v>163</v>
       </c>
       <c r="H138" s="8" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="139" spans="1:8" s="7" customFormat="1">
-      <c r="A139" s="12" t="s">
+    <row r="139" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A139" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="B139" s="12" t="s">
+      <c r="B139" s="10" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C139" s="8" t="s">
+        <v>1067</v>
+      </c>
+      <c r="D139" s="8" t="s">
+        <v>1068</v>
+      </c>
+      <c r="E139" s="8" t="s">
+        <v>1069</v>
+      </c>
+      <c r="F139" s="9" t="s">
         <v>362</v>
-      </c>
-      <c r="C139" s="8" t="s">
-        <v>363</v>
-      </c>
-      <c r="D139" s="8" t="s">
-        <v>364</v>
-      </c>
-      <c r="E139" s="8" t="s">
-        <v>365</v>
-      </c>
-      <c r="F139" s="9" t="s">
-        <v>366</v>
       </c>
       <c r="G139" s="9" t="s">
         <v>164</v>
@@ -8839,50 +9138,50 @@
         <v>137</v>
       </c>
     </row>
-    <row r="140" spans="1:8" s="7" customFormat="1">
-      <c r="A140" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="B140" s="9" t="s">
-        <v>368</v>
-      </c>
-      <c r="C140" s="9" t="s">
-        <v>369</v>
-      </c>
-      <c r="D140" s="9" t="s">
-        <v>370</v>
-      </c>
-      <c r="E140" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="F140" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G140" s="9" t="s">
+    <row r="140" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A140" s="10" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B140" s="10" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C140" s="8" t="s">
+        <v>1070</v>
+      </c>
+      <c r="D140" s="8" t="s">
+        <v>1071</v>
+      </c>
+      <c r="E140" s="8" t="s">
+        <v>1072</v>
+      </c>
+      <c r="F140" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G140" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="H140" s="8" t="s">
+      <c r="H140" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="141" spans="1:8" s="7" customFormat="1">
-      <c r="A141" s="12" t="s">
-        <v>372</v>
-      </c>
-      <c r="B141" s="8" t="s">
-        <v>373</v>
+    <row r="141" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A141" s="10" t="s">
+        <v>1073</v>
+      </c>
+      <c r="B141" s="10" t="s">
+        <v>1074</v>
       </c>
       <c r="C141" s="8" t="s">
-        <v>374</v>
+        <v>1075</v>
       </c>
       <c r="D141" s="8" t="s">
-        <v>375</v>
+        <v>1076</v>
       </c>
       <c r="E141" s="8" t="s">
-        <v>376</v>
+        <v>1077</v>
       </c>
       <c r="F141" s="9" t="s">
-        <v>366</v>
+        <v>1078</v>
       </c>
       <c r="G141" s="9" t="s">
         <v>166</v>
@@ -8891,50 +9190,50 @@
         <v>137</v>
       </c>
     </row>
-    <row r="142" spans="1:8" s="7" customFormat="1">
-      <c r="A142" s="12" t="s">
-        <v>377</v>
-      </c>
-      <c r="B142" s="9" t="s">
-        <v>378</v>
-      </c>
-      <c r="C142" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D142" s="9" t="s">
-        <v>380</v>
-      </c>
-      <c r="E142" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="F142" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G142" s="9" t="s">
+    <row r="142" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A142" s="10" t="s">
+        <v>956</v>
+      </c>
+      <c r="B142" s="10" t="s">
+        <v>966</v>
+      </c>
+      <c r="C142" s="8" t="s">
+        <v>967</v>
+      </c>
+      <c r="D142" s="8" t="s">
+        <v>1079</v>
+      </c>
+      <c r="E142" s="8" t="s">
+        <v>1080</v>
+      </c>
+      <c r="F142" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G142" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="H142" s="8" t="s">
+      <c r="H142" s="9" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="143" spans="1:8" s="7" customFormat="1">
-      <c r="A143" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="B143" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="C143" s="9" t="s">
-        <v>384</v>
-      </c>
-      <c r="D143" s="9" t="s">
-        <v>385</v>
-      </c>
-      <c r="E143" s="9" t="s">
-        <v>386</v>
+    <row r="143" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A143" s="10" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B143" s="10" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C143" s="8" t="s">
+        <v>1084</v>
+      </c>
+      <c r="D143" s="8" t="s">
+        <v>1085</v>
+      </c>
+      <c r="E143" s="8" t="s">
+        <v>1086</v>
       </c>
       <c r="F143" s="9" t="s">
-        <v>366</v>
+        <v>957</v>
       </c>
       <c r="G143" s="9" t="s">
         <v>168</v>
@@ -8943,217 +9242,663 @@
         <v>137</v>
       </c>
     </row>
-    <row r="144" spans="1:8">
-      <c r="A144" s="15" t="s">
+    <row r="144" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A144" s="10" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B144" s="10" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C144" s="8" t="s">
+        <v>1089</v>
+      </c>
+      <c r="D144" s="8" t="s">
+        <v>1090</v>
+      </c>
+      <c r="E144" s="8" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F144" s="9" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G144" s="8" t="s">
+        <v>959</v>
+      </c>
+      <c r="H144" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A145" s="10" t="s">
+        <v>1093</v>
+      </c>
+      <c r="B145" s="10" t="s">
+        <v>1094</v>
+      </c>
+      <c r="C145" s="8" t="s">
+        <v>1095</v>
+      </c>
+      <c r="D145" s="8" t="s">
+        <v>1096</v>
+      </c>
+      <c r="E145" s="8" t="s">
+        <v>1097</v>
+      </c>
+      <c r="F145" s="9" t="s">
+        <v>958</v>
+      </c>
+      <c r="G145" s="9" t="s">
+        <v>960</v>
+      </c>
+      <c r="H145" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="146" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="10" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B146" s="10" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C146" s="8" t="s">
+        <v>1100</v>
+      </c>
+      <c r="D146" s="8" t="s">
+        <v>1101</v>
+      </c>
+      <c r="E146" s="8" t="s">
+        <v>1102</v>
+      </c>
+      <c r="F146" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G146" s="8" t="s">
+        <v>961</v>
+      </c>
+      <c r="H146" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A147" s="10" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B147" s="10" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C147" s="8" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D147" s="8" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E147" s="8" t="s">
+        <v>1108</v>
+      </c>
+      <c r="F147" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G147" s="9" t="s">
+        <v>962</v>
+      </c>
+      <c r="H147" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="10" t="s">
+        <v>1109</v>
+      </c>
+      <c r="B148" s="10" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C148" s="8" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D148" s="8" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E148" s="8" t="s">
+        <v>1113</v>
+      </c>
+      <c r="F148" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G148" s="8" t="s">
+        <v>964</v>
+      </c>
+      <c r="H148" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="149" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A149" s="10" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B149" s="10" t="s">
+        <v>1115</v>
+      </c>
+      <c r="C149" s="8" t="s">
+        <v>1116</v>
+      </c>
+      <c r="D149" s="8" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E149" s="8" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F149" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G149" s="9" t="s">
+        <v>965</v>
+      </c>
+      <c r="H149" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A150" s="10" t="s">
+        <v>1119</v>
+      </c>
+      <c r="B150" s="10" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C150" s="8" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D150" s="8" t="s">
+        <v>1122</v>
+      </c>
+      <c r="E150" s="8" t="s">
+        <v>1123</v>
+      </c>
+      <c r="F150" s="9" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G150" s="8" t="s">
+        <v>970</v>
+      </c>
+      <c r="H150" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="151" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A151" s="10" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B151" s="10" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C151" s="8" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D151" s="8" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E151" s="8" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F151" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G151" s="9" t="s">
+        <v>976</v>
+      </c>
+      <c r="H151" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="152" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="10" t="s">
+        <v>1129</v>
+      </c>
+      <c r="B152" s="10" t="s">
+        <v>1130</v>
+      </c>
+      <c r="C152" s="8" t="s">
+        <v>1131</v>
+      </c>
+      <c r="D152" s="8" t="s">
+        <v>1132</v>
+      </c>
+      <c r="E152" s="8" t="s">
+        <v>1133</v>
+      </c>
+      <c r="F152" s="9" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G152" s="8" t="s">
+        <v>982</v>
+      </c>
+      <c r="H152" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="153" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A153" s="10" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B153" s="10" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C153" s="8" t="s">
+        <v>1136</v>
+      </c>
+      <c r="D153" s="8" t="s">
+        <v>1137</v>
+      </c>
+      <c r="E153" s="8" t="s">
+        <v>1138</v>
+      </c>
+      <c r="F153" s="9" t="s">
+        <v>963</v>
+      </c>
+      <c r="G153" s="9" t="s">
+        <v>988</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A154" s="10" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B154" s="10" t="s">
+        <v>1140</v>
+      </c>
+      <c r="C154" s="8" t="s">
+        <v>1141</v>
+      </c>
+      <c r="D154" s="8" t="s">
+        <v>1142</v>
+      </c>
+      <c r="E154" s="8" t="s">
+        <v>1143</v>
+      </c>
+      <c r="F154" s="9" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G154" s="8" t="s">
+        <v>1063</v>
+      </c>
+      <c r="H154" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="155" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A155" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="C155" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="E155" s="9" t="s">
+        <v>367</v>
+      </c>
+      <c r="F155" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G155" s="9" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H155" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A156" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="B156" s="8" t="s">
+        <v>369</v>
+      </c>
+      <c r="C156" s="8" t="s">
+        <v>370</v>
+      </c>
+      <c r="D156" s="8" t="s">
+        <v>371</v>
+      </c>
+      <c r="E156" s="8" t="s">
+        <v>372</v>
+      </c>
+      <c r="F156" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G156" s="8" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H156" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A157" s="10" t="s">
+        <v>373</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="C157" s="9" t="s">
+        <v>375</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>376</v>
+      </c>
+      <c r="E157" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="F157" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G157" s="9" t="s">
+        <v>1146</v>
+      </c>
+      <c r="H157" s="8" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="158" spans="1:8" s="7" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A158" s="9" t="s">
+        <v>378</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="C158" s="9" t="s">
+        <v>380</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>381</v>
+      </c>
+      <c r="E158" s="9" t="s">
+        <v>382</v>
+      </c>
+      <c r="F158" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G158" s="8" t="s">
+        <v>1147</v>
+      </c>
+      <c r="H158" s="9" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A159" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="B159" s="8" t="s">
+        <v>384</v>
+      </c>
+      <c r="C159" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D159" s="8" t="s">
+        <v>386</v>
+      </c>
+      <c r="E159" s="8" t="s">
         <v>387</v>
       </c>
-      <c r="B144" s="8" t="s">
+      <c r="F159" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H159" s="12" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A160" s="9" t="s">
         <v>388</v>
       </c>
-      <c r="C144" s="8" t="s">
+      <c r="B160" s="9" t="s">
         <v>389</v>
       </c>
-      <c r="D144" s="8" t="s">
+      <c r="C160" s="9" t="s">
         <v>390</v>
       </c>
-      <c r="E144" s="8" t="s">
+      <c r="D160" s="9" t="s">
         <v>391</v>
       </c>
-      <c r="F144" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G144" s="9" t="s">
-        <v>963</v>
-      </c>
-      <c r="H144" s="17" t="s">
+      <c r="E160" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="F160" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G160" s="8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H160" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="145" spans="1:8">
-      <c r="A145" s="16" t="s">
-        <v>392</v>
-      </c>
-      <c r="B145" s="9" t="s">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A161" s="8" t="s">
         <v>393</v>
       </c>
-      <c r="C145" s="9" t="s">
+      <c r="B161" s="8" t="s">
         <v>394</v>
       </c>
-      <c r="D145" s="9" t="s">
+      <c r="C161" s="8" t="s">
         <v>395</v>
       </c>
-      <c r="E145" s="9" t="s">
+      <c r="D161" s="8" t="s">
         <v>396</v>
       </c>
-      <c r="F145" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="G145" s="9" t="s">
-        <v>964</v>
-      </c>
-      <c r="H145" s="17" t="s">
+      <c r="E161" s="8" t="s">
+        <v>397</v>
+      </c>
+      <c r="F161" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G161" s="9" t="s">
+        <v>1150</v>
+      </c>
+      <c r="H161" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="146" spans="1:8">
-      <c r="A146" s="15" t="s">
-        <v>397</v>
-      </c>
-      <c r="B146" s="8" t="s">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A162" s="9" t="s">
         <v>398</v>
       </c>
-      <c r="C146" s="8" t="s">
+      <c r="B162" s="9" t="s">
         <v>399</v>
       </c>
-      <c r="D146" s="8" t="s">
+      <c r="C162" s="9" t="s">
         <v>400</v>
       </c>
-      <c r="E146" s="8" t="s">
+      <c r="D162" s="9" t="s">
         <v>401</v>
       </c>
-      <c r="F146" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G146" s="9" t="s">
-        <v>965</v>
-      </c>
-      <c r="H146" s="17" t="s">
+      <c r="E162" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="F162" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="G162" s="8" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H162" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="147" spans="1:8">
-      <c r="A147" s="16" t="s">
-        <v>402</v>
-      </c>
-      <c r="B147" s="9" t="s">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A163" s="8" t="s">
         <v>403</v>
       </c>
-      <c r="C147" s="9" t="s">
+      <c r="B163" s="8" t="s">
         <v>404</v>
       </c>
-      <c r="D147" s="9" t="s">
+      <c r="C163" s="8" t="s">
         <v>405</v>
       </c>
-      <c r="E147" s="9" t="s">
+      <c r="D163" s="8" t="s">
         <v>406</v>
       </c>
-      <c r="F147" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="G147" s="9" t="s">
-        <v>966</v>
-      </c>
-      <c r="H147" s="17" t="s">
+      <c r="E163" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="F163" s="8" t="s">
+        <v>362</v>
+      </c>
+      <c r="G163" s="9" t="s">
+        <v>1152</v>
+      </c>
+      <c r="H163" s="12" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="148" spans="1:8">
-      <c r="A148" s="15" t="s">
-        <v>407</v>
-      </c>
-      <c r="B148" s="8" t="s">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A164" s="12" t="s">
         <v>408</v>
       </c>
-      <c r="C148" s="8" t="s">
+      <c r="F164" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="D148" s="8" t="s">
+      <c r="G164" s="8" t="s">
+        <v>1153</v>
+      </c>
+      <c r="H164" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A165" s="12" t="s">
         <v>410</v>
       </c>
-      <c r="E148" s="8" t="s">
+      <c r="F165" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="F148" s="8" t="s">
-        <v>366</v>
-      </c>
-      <c r="G148" s="9" t="s">
-        <v>968</v>
-      </c>
-      <c r="H148" s="17" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="149" spans="1:8">
-      <c r="A149" s="17" t="s">
+      <c r="G165" s="9" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H165" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A166" s="12" t="s">
         <v>412</v>
       </c>
-      <c r="F149" s="17" t="s">
+      <c r="F166" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="G149" s="9" t="s">
-        <v>969</v>
-      </c>
-      <c r="H149" s="17" t="s">
+      <c r="G166" s="8" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H166" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="150" spans="1:8">
-      <c r="A150" s="17" t="s">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A167" s="12" t="s">
         <v>414</v>
       </c>
-      <c r="F150" s="17" t="s">
+      <c r="F167" s="12" t="s">
+        <v>356</v>
+      </c>
+      <c r="G167" s="9" t="s">
+        <v>1156</v>
+      </c>
+      <c r="H167" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A168" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="G150" s="9" t="s">
-        <v>974</v>
-      </c>
-      <c r="H150" s="17" t="s">
+      <c r="F168" s="12" t="s">
+        <v>351</v>
+      </c>
+      <c r="G168" s="8" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H168" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="151" spans="1:8">
-      <c r="A151" s="17" t="s">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A169" s="12" t="s">
         <v>416</v>
       </c>
-      <c r="F151" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="G151" s="9" t="s">
-        <v>980</v>
-      </c>
-      <c r="H151" s="17" t="s">
+      <c r="F169" s="12" t="s">
+        <v>349</v>
+      </c>
+      <c r="G169" s="9" t="s">
+        <v>1158</v>
+      </c>
+      <c r="H169" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="152" spans="1:8">
-      <c r="A152" s="17" t="s">
-        <v>418</v>
-      </c>
-      <c r="F152" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="G152" s="9" t="s">
-        <v>986</v>
-      </c>
-      <c r="H152" s="17" t="s">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A170" s="12" t="s">
+        <v>1159</v>
+      </c>
+      <c r="F170" s="12" t="s">
+        <v>1160</v>
+      </c>
+      <c r="G170" s="8" t="s">
+        <v>1167</v>
+      </c>
+      <c r="H170" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
-      <c r="A153" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="F153" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="G153" s="9" t="s">
-        <v>992</v>
-      </c>
-      <c r="H153" s="17" t="s">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A171" s="12" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F171" s="12" t="s">
+        <v>1162</v>
+      </c>
+      <c r="G171" s="9" t="s">
+        <v>1168</v>
+      </c>
+      <c r="H171" s="12" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="154" spans="1:8">
-      <c r="A154" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="F154" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="G154" s="9" t="s">
-        <v>1067</v>
-      </c>
-      <c r="H154" s="17" t="s">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A172" s="12" t="s">
+        <v>1163</v>
+      </c>
+      <c r="F172" s="12" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G172" s="8" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H172" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A173" s="12" t="s">
+        <v>1165</v>
+      </c>
+      <c r="F173" s="12" t="s">
+        <v>1166</v>
+      </c>
+      <c r="G173" s="9" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H173" s="12" t="s">
         <v>144</v>
       </c>
     </row>
@@ -9167,70 +9912,70 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="100" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="18">
+    <row r="1" spans="1:1" ht="18" x14ac:dyDescent="0.4">
       <c r="A1" s="4" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" s="5" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" s="5" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" s="5" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" s="5" t="s">
         <v>156</v>
       </c>
